--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C954C74-1A97-4DE9-BECB-22C5C820619C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C9B7A2-C1F2-4C28-A7B5-AECC7458E636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
-    <sheet name="fuel_prices" sheetId="4" r:id="rId2"/>
-    <sheet name="iea_data" sheetId="2" r:id="rId3"/>
-    <sheet name="ar6_r10" sheetId="3" r:id="rId4"/>
+    <sheet name="DEF" sheetId="5" r:id="rId2"/>
+    <sheet name="fuel_prices" sheetId="4" r:id="rId3"/>
+    <sheet name="iea_data" sheetId="2" r:id="rId4"/>
+    <sheet name="ar6_r10" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">ar6_r10!$A$10:$M$395</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ar6_r10!$A$10:$M$395</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Veda!$B$8:$E$48</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -45,7 +46,7 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="AM8" authorId="0" shapeId="0" xr:uid="{B8774821-523C-49C0-8481-0CFAD2313CD6}">
+    <comment ref="AO8" authorId="0" shapeId="0" xr:uid="{B8774821-523C-49C0-8481-0CFAD2313CD6}">
       <text>
         <r>
           <rPr>
@@ -76,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="147">
   <si>
     <t>C1</t>
   </si>
@@ -441,9 +442,6 @@
     <t>HET</t>
   </si>
   <si>
-    <t>1-8</t>
-  </si>
-  <si>
     <t>chp_heat_twh</t>
   </si>
   <si>
@@ -454,6 +452,72 @@
   </si>
   <si>
     <t>Expensive LNG imports, cheap domestic coal</t>
+  </si>
+  <si>
+    <t>DEF</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>com_pkflx</t>
+  </si>
+  <si>
+    <t>ELC</t>
+  </si>
+  <si>
+    <t>timeslice</t>
+  </si>
+  <si>
+    <t>UC_N</t>
+  </si>
+  <si>
+    <t>UC_RHSRTS</t>
+  </si>
+  <si>
+    <t>DAYNITE</t>
+  </si>
+  <si>
+    <t>UCE_Min-DispatchablePrd</t>
+  </si>
+  <si>
+    <t>UC_RHSRT</t>
+  </si>
+  <si>
+    <t>UCE_Min-DispatchableCAP</t>
+  </si>
+  <si>
+    <t>cset_cn</t>
+  </si>
+  <si>
+    <t>ELC?H</t>
+  </si>
+  <si>
+    <t>Share</t>
+  </si>
+  <si>
+    <t>pset_c0</t>
+  </si>
+  <si>
+    <t>TxCost</t>
+  </si>
+  <si>
+    <t>invcost</t>
+  </si>
+  <si>
+    <t>pset_Set</t>
+  </si>
+  <si>
+    <t>aggregators,grid</t>
+  </si>
+  <si>
+    <t>9-32</t>
   </si>
 </sst>
 </file>
@@ -757,7 +821,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -788,6 +852,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="4" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Bad" xfId="10" builtinId="27"/>
@@ -920,7 +996,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda!$T$17:$Z$17</c:f>
+              <c:f>Veda!$V$17:$AB$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -950,7 +1026,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda!$T$14:$Z$14</c:f>
+              <c:f>Veda!$V$14:$AB$14</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -958,22 +1034,22 @@
                   <c:v>1811.6499999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2264.5625</c:v>
+                  <c:v>2355.145</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2826.174</c:v>
+                  <c:v>2934.873</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3405.9019999999996</c:v>
+                  <c:v>3840.6979999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3949.3969999999999</c:v>
+                  <c:v>4782.7560000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4637.8239999999996</c:v>
+                  <c:v>6213.9594999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5181.3189999999995</c:v>
+                  <c:v>7445.8815000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1208,7 +1284,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda!$I$17:$O$17</c:f>
+              <c:f>Veda!$K$17:$Q$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1238,7 +1314,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda!$I$24:$O$24</c:f>
+              <c:f>Veda!$K$24:$Q$24</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1395,13 +1471,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>454817</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>309562</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>95248</xdr:rowOff>
@@ -1431,13 +1507,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>481012</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>250032</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>76199</xdr:rowOff>
@@ -6000,106 +6076,123 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM85"/>
+  <dimension ref="A1:AO85"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="10.59765625" customWidth="1"/>
-    <col min="7" max="7" width="35.3984375" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="5.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="5.265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="2.73046875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="9.265625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="6.265625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="2.73046875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="2.9296875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.9296875" customWidth="1"/>
+    <col min="2" max="2" width="15.53125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.73046875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7.73046875" customWidth="1"/>
+    <col min="8" max="8" width="10.59765625" customWidth="1"/>
+    <col min="9" max="9" width="35.3984375" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="5.265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="5.265625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.265625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="2.9296875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="G1" s="21" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="I1" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41" x14ac:dyDescent="0.45">
       <c r="D2" s="1" t="str">
-        <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,G1:EE1)</f>
-        <v>~Inputcell: 1-8</v>
-      </c>
-      <c r="K2" s="2" t="s">
+        <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,I1:EG1)</f>
+        <v>~Inputcell: 9-32</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.45">
       <c r="D3" s="9">
-        <v>1</v>
-      </c>
-      <c r="K3" s="10">
+        <v>5</v>
+      </c>
+      <c r="M3" s="10">
         <v>300</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="N3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="P3" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="Q3" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="K4" s="10">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="M4" s="10">
         <v>200</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="N4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="10" t="s">
+      <c r="P4" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="O4" s="10" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="D5" s="1" t="str">
-        <f>VLOOKUP(D3,$C$9:$E$999,2,FALSE)</f>
-        <v>base</v>
-      </c>
-      <c r="E5" s="1">
-        <f>VLOOKUP(D3,$C$9:$E$999,3,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="10">
+      <c r="Q4" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="D5" s="30" t="str">
+        <f>VLOOKUP($D$3,$C$9:$F$999,COLUMN()-2,FALSE)</f>
+        <v>high</v>
+      </c>
+      <c r="E5" s="30">
+        <f>VLOOKUP($D$3,$C$9:$F$999,COLUMN()-2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="30" t="str">
+        <f>VLOOKUP($D$3,$C$9:$F$999,COLUMN()-2,FALSE)</f>
+        <v>Y</v>
+      </c>
+      <c r="G5" s="30">
+        <f>VLOOKUP($D$3,$C$9:$H$999,COLUMN()-2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="M5" s="10">
         <v>100</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="N5" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="K6" s="10">
-        <v>0</v>
-      </c>
-      <c r="L6" s="10" t="s">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="M6" s="10">
+        <v>0</v>
+      </c>
+      <c r="N6" s="10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.45">
       <c r="B7" s="14" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="8" spans="1:39" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+    </row>
+    <row r="8" spans="1:41" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="4" t="s">
         <v>97</v>
       </c>
@@ -6115,17 +6208,23 @@
       <c r="E8" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="AM8" s="2" t="s">
+      <c r="F8" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="AO8" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>5</v>
       </c>
       <c r="B9" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(183),TRUE,D9,TEXT(E9,"$000"))</f>
-        <v>base·$000</v>
+        <f>_xlfn.TEXTJOIN(CHAR(183),TRUE,D9,TEXT(E9,"$000"),F9,TEXT(G9,"000%"))</f>
+        <v>base·$000·Y·100%</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -6136,38 +6235,44 @@
       <c r="E9" s="15">
         <v>0</v>
       </c>
-      <c r="S9" t="s">
+      <c r="F9" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G9" s="33">
+        <v>1</v>
+      </c>
+      <c r="U9" t="s">
         <v>4</v>
       </c>
-      <c r="AG9">
-        <v>1</v>
-      </c>
-      <c r="AH9" t="s">
+      <c r="AI9">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="s">
         <v>85</v>
       </c>
-      <c r="AI9" t="s">
+      <c r="AK9" t="s">
         <v>112</v>
       </c>
-      <c r="AJ9" s="10">
-        <v>1</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="s">
+      <c r="AL9" s="10">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="s">
         <v>87</v>
       </c>
-      <c r="AM9" s="13">
+      <c r="AO9" s="13">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>5</v>
       </c>
       <c r="B10" t="str">
-        <f t="shared" ref="B10:B16" si="0">_xlfn.TEXTJOIN(CHAR(183),TRUE,D10,TEXT(E10,"$000"))</f>
-        <v>base·$100</v>
+        <f t="shared" ref="B10:B40" si="0">_xlfn.TEXTJOIN(CHAR(183),TRUE,D10,TEXT(E10,"$000"),F10,TEXT(G10,"000%"))</f>
+        <v>base·$100·Y·100%</v>
       </c>
       <c r="C10">
         <f>C9+1</f>
@@ -6179,38 +6284,44 @@
       <c r="E10" s="15">
         <v>100</v>
       </c>
-      <c r="S10" s="1">
+      <c r="F10" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G10" s="33">
+        <v>1</v>
+      </c>
+      <c r="U10" s="1">
         <v>2022</v>
       </c>
-      <c r="AG10">
+      <c r="AI10">
         <v>2</v>
       </c>
-      <c r="AH10" t="s">
+      <c r="AJ10" t="s">
         <v>100</v>
       </c>
-      <c r="AI10" t="s">
+      <c r="AK10" t="s">
         <v>111</v>
       </c>
-      <c r="AJ10" s="10">
-        <v>1</v>
-      </c>
-      <c r="AK10" t="s">
+      <c r="AL10" s="10">
+        <v>1</v>
+      </c>
+      <c r="AM10" t="s">
         <v>2</v>
       </c>
-      <c r="AL10" t="s">
+      <c r="AN10" t="s">
         <v>89</v>
       </c>
-      <c r="AM10" s="13">
+      <c r="AO10" s="13">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:39" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:41" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11">
         <v>5</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="0"/>
-        <v>base·$200</v>
+        <v>base·$200·Y·100%</v>
       </c>
       <c r="C11">
         <f>C10+1</f>
@@ -6222,43 +6333,49 @@
       <c r="E11" s="15">
         <v>200</v>
       </c>
-      <c r="S11" s="22">
-        <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,Veda!$S$10)+T28-T29</f>
+      <c r="F11" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G11" s="33">
+        <v>1</v>
+      </c>
+      <c r="U11" s="22">
+        <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,Veda!$U$10)+V28-V29</f>
         <v>1811.6499999999999</v>
       </c>
-      <c r="T11" s="2" t="s">
+      <c r="V11" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="AG11">
+      <c r="AI11">
         <v>3</v>
       </c>
-      <c r="AH11" t="s">
+      <c r="AJ11" t="s">
         <v>98</v>
       </c>
-      <c r="AI11" t="str">
-        <f>AH11</f>
+      <c r="AK11" t="str">
+        <f>AJ11</f>
         <v>ts_012</v>
       </c>
-      <c r="AJ11" s="10">
-        <v>1</v>
-      </c>
-      <c r="AK11" t="s">
+      <c r="AL11" s="10">
+        <v>1</v>
+      </c>
+      <c r="AM11" t="s">
         <v>5</v>
       </c>
-      <c r="AL11" t="s">
+      <c r="AN11" t="s">
         <v>90</v>
       </c>
-      <c r="AM11" s="13">
+      <c r="AO11" s="13">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:39" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:41" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12">
         <v>5</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="0"/>
-        <v>base·$300</v>
+        <v>base·$300·Y·100%</v>
       </c>
       <c r="C12">
         <f>C11+1</f>
@@ -6270,40 +6387,46 @@
       <c r="E12" s="15">
         <v>300</v>
       </c>
-      <c r="S12" s="22">
-        <f>SUMIFS(iea_data!J3:J9999,iea_data!$B$3:$B$9999,Veda!$S$10)</f>
-        <v>0</v>
-      </c>
-      <c r="AG12">
+      <c r="F12" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G12" s="33">
+        <v>1</v>
+      </c>
+      <c r="U12" s="22">
+        <f>SUMIFS(iea_data!J3:J9999,iea_data!$B$3:$B$9999,Veda!$U$10)</f>
+        <v>0</v>
+      </c>
+      <c r="AI12">
         <v>4</v>
       </c>
-      <c r="AH12" t="s">
+      <c r="AJ12" t="s">
         <v>104</v>
       </c>
-      <c r="AI12" t="str">
-        <f t="shared" ref="AI12:AI16" si="1">AH12</f>
+      <c r="AK12" t="str">
+        <f t="shared" ref="AK12:AK16" si="1">AJ12</f>
         <v>ts_030</v>
       </c>
-      <c r="AJ12" s="10">
-        <v>1</v>
-      </c>
-      <c r="AK12" t="s">
+      <c r="AL12" s="10">
+        <v>1</v>
+      </c>
+      <c r="AM12" t="s">
         <v>7</v>
       </c>
-      <c r="AL12" t="s">
+      <c r="AN12" t="s">
         <v>91</v>
       </c>
-      <c r="AM12" s="13">
+      <c r="AO12" s="13">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:39" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:41" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>5</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="0"/>
-        <v>high·$000</v>
+        <v>high·$000·Y·100%</v>
       </c>
       <c r="C13">
         <f>C12+1</f>
@@ -6316,39 +6439,45 @@
         <f>E9</f>
         <v>0</v>
       </c>
-      <c r="AG13">
+      <c r="F13" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G13" s="33">
+        <v>1</v>
+      </c>
+      <c r="AI13">
         <v>5</v>
       </c>
-      <c r="AH13" t="s">
+      <c r="AJ13" t="s">
         <v>99</v>
       </c>
-      <c r="AI13" t="str">
+      <c r="AK13" t="str">
         <f t="shared" si="1"/>
         <v>ts_048</v>
       </c>
-      <c r="AJ13" s="10">
-        <v>1</v>
-      </c>
-      <c r="AK13" t="s">
+      <c r="AL13" s="10">
+        <v>1</v>
+      </c>
+      <c r="AM13" t="s">
         <v>9</v>
       </c>
-      <c r="AL13" t="s">
+      <c r="AN13" t="s">
         <v>92</v>
       </c>
-      <c r="AM13" s="13">
+      <c r="AO13" s="13">
         <v>1.5</v>
       </c>
     </row>
-    <row r="14" spans="1:39" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:41" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14">
         <v>5</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="0"/>
-        <v>high·$100</v>
+        <v>high·$100·Y·100%</v>
       </c>
       <c r="C14">
-        <f t="shared" ref="C14:C16" si="2">C13+1</f>
+        <f t="shared" ref="C14:C40" si="2">C13+1</f>
         <v>6</v>
       </c>
       <c r="D14" t="s">
@@ -6358,91 +6487,97 @@
         <f t="shared" ref="E14:E16" si="3">E10</f>
         <v>100</v>
       </c>
-      <c r="G14" t="s">
+      <c r="F14" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G14" s="33">
+        <v>1</v>
+      </c>
+      <c r="I14" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="3" t="str">
-        <f>VLOOKUP($D$5,$N$3:$O$5,2,FALSE)</f>
-        <v>C4</v>
-      </c>
-      <c r="I14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$E$5,ar6_r10!$C$2:$C$999,Veda!I$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
-        <v>1.25</v>
+      <c r="J14" s="3" t="str">
+        <f>VLOOKUP($D$5,$P$3:$Q$5,2,FALSE)</f>
+        <v>C3</v>
       </c>
       <c r="K14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
-        <v>1.56</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$E$5,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
+        <v>0</v>
       </c>
       <c r="L14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
-        <v>1.88</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
+        <v>1.3</v>
       </c>
       <c r="M14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
-        <v>2.1800000000000002</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
+        <v>1.62</v>
       </c>
       <c r="N14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
-        <v>2.56</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
+        <v>2.12</v>
       </c>
       <c r="O14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G14)</f>
-        <v>2.86</v>
-      </c>
-      <c r="T14" s="8">
-        <f>S11</f>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
+        <v>2.64</v>
+      </c>
+      <c r="P14" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
+        <v>3.43</v>
+      </c>
+      <c r="Q14" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="V14" s="8">
+        <f>U11</f>
         <v>1811.6499999999999</v>
       </c>
-      <c r="U14" s="8">
-        <f t="shared" ref="U14:Z14" si="4">$S$11*J14</f>
-        <v>2264.5625</v>
-      </c>
-      <c r="V14" s="8">
-        <f t="shared" si="4"/>
-        <v>2826.174</v>
-      </c>
       <c r="W14" s="8">
-        <f t="shared" si="4"/>
-        <v>3405.9019999999996</v>
+        <f t="shared" ref="W14:AB14" si="4">$U$11*L14</f>
+        <v>2355.145</v>
       </c>
       <c r="X14" s="8">
         <f t="shared" si="4"/>
-        <v>3949.3969999999999</v>
+        <v>2934.873</v>
       </c>
       <c r="Y14" s="8">
         <f t="shared" si="4"/>
-        <v>4637.8239999999996</v>
+        <v>3840.6979999999999</v>
       </c>
       <c r="Z14" s="8">
         <f t="shared" si="4"/>
-        <v>5181.3189999999995</v>
-      </c>
-      <c r="AG14">
+        <v>4782.7560000000003</v>
+      </c>
+      <c r="AA14" s="8">
+        <f t="shared" si="4"/>
+        <v>6213.9594999999999</v>
+      </c>
+      <c r="AB14" s="8">
+        <f t="shared" si="4"/>
+        <v>7445.8815000000004</v>
+      </c>
+      <c r="AI14">
         <v>6</v>
       </c>
-      <c r="AH14" t="s">
+      <c r="AJ14" t="s">
         <v>108</v>
       </c>
-      <c r="AI14" t="str">
+      <c r="AK14" t="str">
         <f t="shared" si="1"/>
         <v>ts_072</v>
       </c>
-      <c r="AJ14" s="10">
-        <f>AJ9+1</f>
+      <c r="AL14" s="10">
+        <f>AL9+1</f>
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:39" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:41" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>5</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="0"/>
-        <v>high·$200</v>
+        <v>high·$200·Y·100%</v>
       </c>
       <c r="C15">
         <f t="shared" si="2"/>
@@ -6455,59 +6590,65 @@
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="G15" t="s">
+      <c r="F15" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G15" s="33">
+        <v>1</v>
+      </c>
+      <c r="I15" t="s">
         <v>113</v>
       </c>
-      <c r="I15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$E$5,ar6_r10!$C$2:$C$999,Veda!I$17,ar6_r10!$M$2:$M$999,Veda!$G15)</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G15)</f>
+      <c r="K15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$E$5,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
         <v>2.33</v>
       </c>
-      <c r="K15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G15)</f>
+      <c r="M15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
         <v>4.4000000000000004</v>
       </c>
-      <c r="L15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G15)</f>
+      <c r="N15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
         <v>7.61</v>
       </c>
-      <c r="M15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G15)</f>
-        <v>11.82</v>
-      </c>
-      <c r="N15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G15)</f>
+      <c r="O15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
+        <v>11.44</v>
+      </c>
+      <c r="P15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
         <v>19.03</v>
       </c>
-      <c r="O15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G15)</f>
-        <v>30.24</v>
-      </c>
-      <c r="AG15">
+      <c r="Q15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
+        <v>25.28</v>
+      </c>
+      <c r="AI15">
         <v>7</v>
       </c>
-      <c r="AH15" t="s">
+      <c r="AJ15" t="s">
         <v>109</v>
       </c>
-      <c r="AI15" t="str">
+      <c r="AK15" t="str">
         <f t="shared" si="1"/>
         <v>ts_144</v>
       </c>
-      <c r="AJ15" s="10">
-        <f t="shared" ref="AJ15:AJ78" si="5">AJ10+1</f>
+      <c r="AL15" s="10">
+        <f t="shared" ref="AL15:AL78" si="5">AL10+1</f>
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:39" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:41" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A16">
         <v>5</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="0"/>
-        <v>high·$300</v>
+        <v>high·$300·Y·100%</v>
       </c>
       <c r="C16">
         <f t="shared" si="2"/>
@@ -6520,141 +6661,182 @@
         <f t="shared" si="3"/>
         <v>300</v>
       </c>
-      <c r="S16" s="5" t="s">
+      <c r="F16" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G16" s="33">
+        <v>1</v>
+      </c>
+      <c r="U16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AG16">
+      <c r="AI16">
         <v>8</v>
       </c>
-      <c r="AH16" t="s">
+      <c r="AJ16" t="s">
         <v>110</v>
       </c>
-      <c r="AI16" t="str">
+      <c r="AK16" t="str">
         <f t="shared" si="1"/>
         <v>ts_288</v>
       </c>
-      <c r="AJ16" s="10">
+      <c r="AL16" s="10">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:38" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A17">
         <v>5</v>
       </c>
-      <c r="I17" s="7">
+      <c r="B17" t="str">
+        <f t="shared" si="0"/>
+        <v>base·$000·N·100%</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="D17" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G17" s="33">
+        <v>1</v>
+      </c>
+      <c r="K17" s="7">
         <v>2020</v>
       </c>
-      <c r="J17" s="7">
-        <f t="shared" ref="J17:O17" si="6">U17</f>
+      <c r="L17" s="7">
+        <f t="shared" ref="L17:Q17" si="6">W17</f>
         <v>2025</v>
       </c>
-      <c r="K17" s="7">
+      <c r="M17" s="7">
         <f t="shared" si="6"/>
         <v>2030</v>
       </c>
-      <c r="L17" s="7">
+      <c r="N17" s="7">
         <f t="shared" si="6"/>
         <v>2035</v>
       </c>
-      <c r="M17" s="7">
+      <c r="O17" s="7">
         <f t="shared" si="6"/>
         <v>2040</v>
       </c>
-      <c r="N17" s="7">
+      <c r="P17" s="7">
         <f t="shared" si="6"/>
         <v>2045</v>
       </c>
-      <c r="O17" s="7">
+      <c r="Q17" s="7">
         <f t="shared" si="6"/>
         <v>2050</v>
       </c>
-      <c r="S17" s="4" t="s">
+      <c r="U17" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="T17" s="4">
+      <c r="V17" s="4">
         <v>2022</v>
       </c>
-      <c r="U17" s="4">
+      <c r="W17" s="4">
         <v>2025</v>
       </c>
-      <c r="V17" s="4">
+      <c r="X17" s="4">
         <v>2030</v>
       </c>
-      <c r="W17" s="4">
+      <c r="Y17" s="4">
         <v>2035</v>
       </c>
-      <c r="X17" s="4">
+      <c r="Z17" s="4">
         <v>2040</v>
       </c>
-      <c r="Y17" s="4">
+      <c r="AA17" s="4">
         <v>2045</v>
       </c>
-      <c r="Z17" s="4">
+      <c r="AB17" s="4">
         <v>2050</v>
       </c>
-      <c r="AA17" s="4" t="s">
+      <c r="AC17" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="AG17">
+      <c r="AI17">
         <v>9</v>
       </c>
-      <c r="AH17" t="s">
+      <c r="AJ17" t="s">
         <v>103</v>
       </c>
-      <c r="AI17" t="s">
+      <c r="AK17" t="s">
         <v>105</v>
       </c>
-      <c r="AJ17" s="10">
+      <c r="AL17" s="10">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="G18" t="s">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <v>5</v>
+      </c>
+      <c r="B18" t="str">
+        <f t="shared" si="0"/>
+        <v>base·$100·N·100%</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="D18" t="s">
+        <v>114</v>
+      </c>
+      <c r="E18" s="15">
+        <v>100</v>
+      </c>
+      <c r="F18" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G18" s="33">
+        <v>1</v>
+      </c>
+      <c r="I18" t="s">
         <v>15</v>
       </c>
-      <c r="I18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!I$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
-        <v>0</v>
-      </c>
       <c r="K18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I18)</f>
         <v>0</v>
       </c>
       <c r="L18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I18)</f>
         <v>0</v>
       </c>
       <c r="M18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I18)</f>
         <v>0</v>
       </c>
       <c r="N18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I18)</f>
         <v>0.01</v>
       </c>
       <c r="O18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G18)</f>
-        <v>0.01</v>
-      </c>
-      <c r="S18" s="10" t="s">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I18)</f>
+        <v>0.02</v>
+      </c>
+      <c r="P18" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I18)</f>
+        <v>0.02</v>
+      </c>
+      <c r="Q18" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I18)</f>
+        <v>0.03</v>
+      </c>
+      <c r="U18" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="T18" s="6">
-        <f t="shared" ref="T18:Z20" si="7">I18*T$14</f>
-        <v>0</v>
-      </c>
-      <c r="U18" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
       <c r="V18" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="V18:AB20" si="7">K18*V$14</f>
         <v>0</v>
       </c>
       <c r="W18" s="6">
@@ -6667,239 +6849,309 @@
       </c>
       <c r="Y18" s="6">
         <f t="shared" si="7"/>
-        <v>46.378239999999998</v>
+        <v>38.406979999999997</v>
       </c>
       <c r="Z18" s="6">
         <f t="shared" si="7"/>
-        <v>51.813189999999999</v>
-      </c>
-      <c r="AA18" t="s">
+        <v>95.655120000000011</v>
+      </c>
+      <c r="AA18" s="6">
+        <f t="shared" si="7"/>
+        <v>124.27919</v>
+      </c>
+      <c r="AB18" s="6">
+        <f t="shared" si="7"/>
+        <v>223.37644500000002</v>
+      </c>
+      <c r="AC18" t="s">
         <v>17</v>
       </c>
-      <c r="AC18" s="2"/>
-      <c r="AG18">
+      <c r="AE18" s="2"/>
+      <c r="AI18">
         <v>10</v>
       </c>
-      <c r="AH18" t="s">
+      <c r="AJ18" t="s">
         <v>106</v>
       </c>
-      <c r="AI18" t="s">
+      <c r="AK18" t="s">
         <v>107</v>
       </c>
-      <c r="AJ18" s="10">
+      <c r="AL18" s="10">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="G19" t="s">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>5</v>
+      </c>
+      <c r="B19" t="str">
+        <f t="shared" si="0"/>
+        <v>base·$200·N·100%</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" s="15">
+        <v>200</v>
+      </c>
+      <c r="F19" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G19" s="33">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
         <v>18</v>
       </c>
-      <c r="I19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!I$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
+      <c r="K19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
+        <v>0.49</v>
+      </c>
+      <c r="L19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
+        <v>0.49</v>
+      </c>
+      <c r="M19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
+        <v>0.46</v>
+      </c>
+      <c r="N19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
+        <v>0.48</v>
+      </c>
+      <c r="O19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
+        <v>0.46</v>
+      </c>
+      <c r="P19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
+        <v>0.48</v>
+      </c>
+      <c r="Q19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
         <v>0.47</v>
       </c>
-      <c r="J19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
-        <v>0.46</v>
-      </c>
-      <c r="K19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
-        <v>0.41</v>
-      </c>
-      <c r="L19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
-        <v>0.44</v>
-      </c>
-      <c r="M19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
-        <v>0.42</v>
-      </c>
-      <c r="N19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
-        <v>0.42</v>
-      </c>
-      <c r="O19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G19)</f>
-        <v>0.43</v>
-      </c>
-      <c r="S19" s="10" t="s">
+      <c r="U19" s="10" t="s">
         <v>19</v>
-      </c>
-      <c r="T19" s="6">
-        <f t="shared" si="7"/>
-        <v>851.4754999999999</v>
-      </c>
-      <c r="U19" s="6">
-        <f t="shared" si="7"/>
-        <v>1041.69875</v>
       </c>
       <c r="V19" s="6">
         <f t="shared" si="7"/>
-        <v>1158.7313399999998</v>
+        <v>887.70849999999996</v>
       </c>
       <c r="W19" s="6">
         <f t="shared" si="7"/>
-        <v>1498.5968799999998</v>
+        <v>1154.0210500000001</v>
       </c>
       <c r="X19" s="6">
         <f t="shared" si="7"/>
-        <v>1658.7467399999998</v>
+        <v>1350.0415800000001</v>
       </c>
       <c r="Y19" s="6">
         <f t="shared" si="7"/>
-        <v>1947.8860799999998</v>
+        <v>1843.5350399999998</v>
       </c>
       <c r="Z19" s="6">
         <f t="shared" si="7"/>
-        <v>2227.9671699999999</v>
-      </c>
-      <c r="AA19" t="s">
+        <v>2200.0677600000004</v>
+      </c>
+      <c r="AA19" s="6">
+        <f t="shared" si="7"/>
+        <v>2982.7005599999998</v>
+      </c>
+      <c r="AB19" s="6">
+        <f t="shared" si="7"/>
+        <v>3499.5643049999999</v>
+      </c>
+      <c r="AC19" t="s">
         <v>17</v>
       </c>
-      <c r="AG19">
+      <c r="AI19">
         <v>11</v>
       </c>
-      <c r="AH19" t="s">
+      <c r="AJ19" t="s">
         <v>83</v>
       </c>
-      <c r="AI19" t="s">
+      <c r="AK19" t="s">
         <v>88</v>
       </c>
-      <c r="AJ19" s="10">
+      <c r="AL19" s="10">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="G20" t="s">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>5</v>
+      </c>
+      <c r="B20" t="str">
+        <f t="shared" si="0"/>
+        <v>base·$300·N·100%</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="15">
+        <v>300</v>
+      </c>
+      <c r="F20" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G20" s="33">
+        <v>1</v>
+      </c>
+      <c r="I20" t="s">
         <v>21</v>
       </c>
-      <c r="I20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!I$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
-        <v>0.4</v>
-      </c>
-      <c r="J20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
+      <c r="K20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
         <v>0.46</v>
       </c>
-      <c r="K20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
-        <v>0.46</v>
-      </c>
       <c r="L20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
-        <v>0.46</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
+        <v>0.47</v>
       </c>
       <c r="M20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
-        <v>0.48</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
+        <v>0.45</v>
       </c>
       <c r="N20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
-        <v>0.48</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
+        <v>0.45</v>
       </c>
       <c r="O20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G20)</f>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
         <v>0.47</v>
       </c>
-      <c r="S20" s="10" t="s">
+      <c r="P20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
+        <v>0.44</v>
+      </c>
+      <c r="Q20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
+        <v>0.44</v>
+      </c>
+      <c r="U20" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="T20" s="6">
-        <f t="shared" si="7"/>
-        <v>724.66</v>
-      </c>
-      <c r="U20" s="6">
-        <f t="shared" si="7"/>
-        <v>1041.69875</v>
       </c>
       <c r="V20" s="6">
         <f t="shared" si="7"/>
-        <v>1300.0400400000001</v>
+        <v>833.35899999999992</v>
       </c>
       <c r="W20" s="6">
         <f t="shared" si="7"/>
-        <v>1566.7149199999999</v>
+        <v>1106.91815</v>
       </c>
       <c r="X20" s="6">
         <f t="shared" si="7"/>
-        <v>1895.71056</v>
+        <v>1320.6928500000001</v>
       </c>
       <c r="Y20" s="6">
         <f t="shared" si="7"/>
-        <v>2226.1555199999998</v>
+        <v>1728.3141000000001</v>
       </c>
       <c r="Z20" s="6">
         <f t="shared" si="7"/>
-        <v>2435.2199299999997</v>
-      </c>
-      <c r="AA20" t="s">
+        <v>2247.8953200000001</v>
+      </c>
+      <c r="AA20" s="6">
+        <f t="shared" si="7"/>
+        <v>2734.1421799999998</v>
+      </c>
+      <c r="AB20" s="6">
+        <f t="shared" si="7"/>
+        <v>3276.18786</v>
+      </c>
+      <c r="AC20" t="s">
         <v>17</v>
       </c>
-      <c r="AG20">
+      <c r="AI20">
         <v>12</v>
       </c>
-      <c r="AH20" t="s">
+      <c r="AJ20" t="s">
         <v>84</v>
       </c>
-      <c r="AI20" t="s">
+      <c r="AK20" t="s">
         <v>93</v>
       </c>
-      <c r="AJ20" s="10">
+      <c r="AL20" s="10">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="G21" t="s">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>5</v>
+      </c>
+      <c r="B21" t="str">
+        <f t="shared" si="0"/>
+        <v>high·$000·N·100%</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="D21" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" s="15">
+        <f>E17</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" s="33">
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
         <v>23</v>
       </c>
-      <c r="I21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!I$17,ar6_r10!$M$2:$M$999,Veda!$G21)</f>
+      <c r="K21" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I21)</f>
         <v>0.02</v>
       </c>
-      <c r="J21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G21)</f>
+      <c r="L21" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I21)</f>
         <v>0.02</v>
       </c>
-      <c r="K21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G21)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G21)</f>
+      <c r="M21" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I21)</f>
         <v>0.03</v>
       </c>
-      <c r="M21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G21)</f>
+      <c r="N21" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I21)</f>
         <v>0.04</v>
       </c>
-      <c r="N21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G21)</f>
-        <v>0.04</v>
-      </c>
       <c r="O21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G21)</f>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I21)</f>
         <v>0.05</v>
       </c>
-      <c r="S21" s="10" t="s">
+      <c r="P21" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I21)</f>
+        <v>0.06</v>
+      </c>
+      <c r="Q21" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I21)</f>
+        <v>0.06</v>
+      </c>
+      <c r="U21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="T21" s="6">
-        <f>I21*T$14</f>
+      <c r="V21" s="6">
+        <f>K21*V$14</f>
         <v>36.232999999999997</v>
       </c>
-      <c r="U21" s="6">
-        <f t="shared" ref="U21:Z21" si="8">T21</f>
-        <v>36.232999999999997</v>
-      </c>
-      <c r="V21" s="6">
-        <f t="shared" si="8"/>
-        <v>36.232999999999997</v>
-      </c>
       <c r="W21" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="W21:AB21" si="8">V21</f>
         <v>36.232999999999997</v>
       </c>
       <c r="X21" s="6">
@@ -6914,144 +7166,216 @@
         <f t="shared" si="8"/>
         <v>36.232999999999997</v>
       </c>
-      <c r="AA21" t="s">
+      <c r="AA21" s="6">
+        <f t="shared" si="8"/>
+        <v>36.232999999999997</v>
+      </c>
+      <c r="AB21" s="6">
+        <f t="shared" si="8"/>
+        <v>36.232999999999997</v>
+      </c>
+      <c r="AC21" t="s">
         <v>17</v>
       </c>
-      <c r="AC21" s="2" t="s">
+      <c r="AE21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AJ21" s="10">
+      <c r="AL21" s="10">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="S22" s="10" t="s">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>5</v>
+      </c>
+      <c r="B22" t="str">
+        <f t="shared" si="0"/>
+        <v>high·$100·N·100%</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" s="15">
+        <f t="shared" ref="E22:E24" si="9">E18</f>
+        <v>100</v>
+      </c>
+      <c r="F22" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G22" s="33">
+        <v>1</v>
+      </c>
+      <c r="U22" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="T22" s="6">
-        <f t="shared" ref="T22:Z22" si="9">T14-SUM(T19:T21)</f>
-        <v>199.28150000000005</v>
-      </c>
-      <c r="U22" s="6">
-        <f t="shared" si="9"/>
-        <v>144.93199999999979</v>
-      </c>
       <c r="V22" s="6">
-        <f t="shared" si="9"/>
-        <v>331.16961999999967</v>
+        <f t="shared" ref="V22:AB22" si="10">V14-SUM(V19:V21)</f>
+        <v>54.349500000000035</v>
       </c>
       <c r="W22" s="6">
-        <f t="shared" si="9"/>
-        <v>304.35719999999992</v>
+        <f t="shared" si="10"/>
+        <v>57.972800000000007</v>
       </c>
       <c r="X22" s="6">
-        <f t="shared" si="9"/>
-        <v>358.70669999999973</v>
+        <f t="shared" si="10"/>
+        <v>227.90556999999944</v>
       </c>
       <c r="Y22" s="6">
-        <f t="shared" si="9"/>
-        <v>427.54939999999988</v>
+        <f t="shared" si="10"/>
+        <v>232.61585999999988</v>
       </c>
       <c r="Z22" s="6">
-        <f t="shared" si="9"/>
-        <v>481.89890000000014</v>
-      </c>
-      <c r="AA22" t="s">
+        <f t="shared" si="10"/>
+        <v>298.55991999999969</v>
+      </c>
+      <c r="AA22" s="6">
+        <f t="shared" si="10"/>
+        <v>460.88375999999971</v>
+      </c>
+      <c r="AB22" s="6">
+        <f t="shared" si="10"/>
+        <v>633.89633500000036</v>
+      </c>
+      <c r="AC22" t="s">
         <v>17</v>
       </c>
-      <c r="AJ22" s="10">
+      <c r="AL22" s="10">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="S23" s="23" t="s">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>5</v>
+      </c>
+      <c r="B23" t="str">
+        <f t="shared" si="0"/>
+        <v>high·$200·N·100%</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="D23" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="15">
+        <f t="shared" si="9"/>
+        <v>200</v>
+      </c>
+      <c r="F23" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G23" s="33">
+        <v>1</v>
+      </c>
+      <c r="U23" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="T23" s="24">
-        <f>S12</f>
-        <v>0</v>
-      </c>
-      <c r="U23" s="25">
-        <f>$S$12*J15</f>
-        <v>0</v>
-      </c>
-      <c r="V23" s="25">
-        <f>$S$12*K15</f>
+      <c r="V23" s="24">
+        <f>U12</f>
         <v>0</v>
       </c>
       <c r="W23" s="25">
-        <f t="shared" ref="W23:Z23" si="10">$S$12*L15</f>
+        <f>$U$12*L15</f>
         <v>0</v>
       </c>
       <c r="X23" s="25">
-        <f t="shared" si="10"/>
+        <f>$U$12*M15</f>
         <v>0</v>
       </c>
       <c r="Y23" s="25">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="Y23:AB23" si="11">$U$12*N15</f>
         <v>0</v>
       </c>
       <c r="Z23" s="25">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AA23" s="23" t="s">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AA23" s="25">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB23" s="25">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AC23" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="AJ23" s="10">
+      <c r="AL23" s="10">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:36" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="G24" s="10" t="s">
+    <row r="24" spans="1:38" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A24">
+        <v>5</v>
+      </c>
+      <c r="B24" t="str">
+        <f t="shared" si="0"/>
+        <v>high·$300·N·100%</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="D24" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="15">
+        <f t="shared" si="9"/>
+        <v>300</v>
+      </c>
+      <c r="F24" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G24" s="33">
+        <v>1</v>
+      </c>
+      <c r="I24" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="H24" s="3" t="str">
-        <f>VLOOKUP(E5,$K$3:$L$6,2,FALSE)</f>
+      <c r="J24" s="3" t="str">
+        <f>VLOOKUP(E5,$M$3:$N$6,2,FALSE)</f>
         <v>C7</v>
       </c>
-      <c r="I24" s="8">
-        <v>0</v>
-      </c>
-      <c r="J24" s="8">
-        <v>0</v>
-      </c>
       <c r="K24" s="8">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$24,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G24)</f>
         <v>0</v>
       </c>
       <c r="L24" s="8">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$24,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G24)</f>
         <v>0</v>
       </c>
       <c r="M24" s="8">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$24,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G24)</f>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$24,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I24)</f>
         <v>0</v>
       </c>
       <c r="N24" s="8">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$24,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G24)</f>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$24,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I24)</f>
         <v>0</v>
       </c>
       <c r="O24" s="8">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$24,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G24)</f>
-        <v>0</v>
-      </c>
-      <c r="S24" s="26" t="s">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$24,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I24)</f>
+        <v>0</v>
+      </c>
+      <c r="P24" s="8">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$24,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I24)</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="8">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$24,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I24)</f>
+        <v>0</v>
+      </c>
+      <c r="U24" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="T24" s="27"/>
-      <c r="U24" s="27">
-        <v>0</v>
-      </c>
-      <c r="V24" s="28">
-        <f>K24/1000</f>
-        <v>0</v>
-      </c>
-      <c r="W24" s="28">
-        <f>L24/1000</f>
+      <c r="V24" s="27"/>
+      <c r="W24" s="27">
         <v>0</v>
       </c>
       <c r="X24" s="28">
@@ -7066,749 +7390,1133 @@
         <f>O24/1000</f>
         <v>0</v>
       </c>
-      <c r="AA24" s="29" t="s">
+      <c r="AA24" s="28">
+        <f>P24/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AB24" s="28">
+        <f>Q24/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AC24" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="AJ24" s="10">
+      <c r="AL24" s="10">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:36" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="AJ25" s="10">
+    <row r="25" spans="1:38" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <v>5</v>
+      </c>
+      <c r="B25" t="str">
+        <f t="shared" si="0"/>
+        <v>base·$000·Y·001%</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="D25" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" s="15">
+        <v>0</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G25" s="33">
+        <v>0.01</v>
+      </c>
+      <c r="AL25" s="10">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:36" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="S26" s="5" t="s">
+    <row r="26" spans="1:38" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A26">
+        <v>5</v>
+      </c>
+      <c r="B26" t="str">
+        <f t="shared" si="0"/>
+        <v>base·$100·Y·001%</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="D26" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" s="15">
+        <v>100</v>
+      </c>
+      <c r="F26" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G26" s="33">
+        <v>0.01</v>
+      </c>
+      <c r="U26" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AJ26" s="10">
+      <c r="AL26" s="10">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:36" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="S27" s="4" t="s">
+    <row r="27" spans="1:38" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A27">
+        <v>5</v>
+      </c>
+      <c r="B27" t="str">
+        <f t="shared" si="0"/>
+        <v>base·$200·Y·001%</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="D27" t="s">
+        <v>114</v>
+      </c>
+      <c r="E27" s="15">
+        <v>200</v>
+      </c>
+      <c r="F27" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" s="33">
+        <v>0.01</v>
+      </c>
+      <c r="U27" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="T27" s="4">
-        <f t="shared" ref="T27:Z27" si="11">T17</f>
+      <c r="V27" s="4">
+        <f t="shared" ref="V27:AB27" si="12">V17</f>
         <v>2022</v>
       </c>
-      <c r="U27" s="4">
-        <f t="shared" si="11"/>
+      <c r="W27" s="4">
+        <f t="shared" si="12"/>
         <v>2025</v>
       </c>
-      <c r="V27" s="4">
-        <f t="shared" si="11"/>
+      <c r="X27" s="4">
+        <f t="shared" si="12"/>
         <v>2030</v>
       </c>
-      <c r="W27" s="4">
-        <f t="shared" si="11"/>
+      <c r="Y27" s="4">
+        <f t="shared" si="12"/>
         <v>2035</v>
       </c>
-      <c r="X27" s="4">
-        <f t="shared" si="11"/>
+      <c r="Z27" s="4">
+        <f t="shared" si="12"/>
         <v>2040</v>
       </c>
-      <c r="Y27" s="4">
-        <f t="shared" si="11"/>
+      <c r="AA27" s="4">
+        <f t="shared" si="12"/>
         <v>2045</v>
       </c>
-      <c r="Z27" s="4">
-        <f t="shared" si="11"/>
+      <c r="AB27" s="4">
+        <f t="shared" si="12"/>
         <v>2050</v>
       </c>
-      <c r="AA27" s="4" t="s">
+      <c r="AC27" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="AB27" s="4" t="s">
+      <c r="AD27" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AJ27" s="10">
+      <c r="AL27" s="10">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:36" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="Q28" s="3">
-        <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,Veda!$S$10)</f>
+    <row r="28" spans="1:38" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A28">
+        <v>5</v>
+      </c>
+      <c r="B28" t="str">
+        <f t="shared" si="0"/>
+        <v>base·$300·Y·001%</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="D28" t="s">
+        <v>114</v>
+      </c>
+      <c r="E28" s="15">
+        <v>300</v>
+      </c>
+      <c r="F28" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G28" s="33">
+        <v>0.01</v>
+      </c>
+      <c r="S28" s="3">
+        <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,Veda!$U$10)</f>
         <v>7.84</v>
       </c>
-      <c r="S28" t="s">
+      <c r="U28" t="s">
         <v>31</v>
       </c>
-      <c r="T28" s="3">
-        <f>Q28</f>
+      <c r="V28" s="3">
+        <f>S28</f>
         <v>7.84</v>
       </c>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
       <c r="X28" s="6"/>
       <c r="Y28" s="6"/>
       <c r="Z28" s="6"/>
-      <c r="AA28" t="s">
+      <c r="AA28" s="6"/>
+      <c r="AB28" s="6"/>
+      <c r="AC28" t="s">
         <v>32</v>
       </c>
-      <c r="AB28" t="s">
+      <c r="AD28" t="s">
         <v>33</v>
       </c>
-      <c r="AJ28" s="10">
+      <c r="AL28" s="10">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:36" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="Q29" s="3">
-        <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,Veda!$S$10)</f>
+    <row r="29" spans="1:38" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A29">
+        <v>5</v>
+      </c>
+      <c r="B29" t="str">
+        <f t="shared" si="0"/>
+        <v>high·$000·Y·001%</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="D29" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" s="15">
+        <f>E25</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G29" s="33">
+        <v>0.01</v>
+      </c>
+      <c r="S29" s="3">
+        <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,Veda!$U$10)</f>
         <v>-10.25</v>
       </c>
-      <c r="S29" t="s">
+      <c r="U29" t="s">
         <v>34</v>
       </c>
-      <c r="T29" s="3">
-        <f>-1*Q29</f>
+      <c r="V29" s="3">
+        <f>-1*S29</f>
         <v>10.25</v>
       </c>
-      <c r="V29" s="6"/>
-      <c r="W29" s="6"/>
       <c r="X29" s="6"/>
       <c r="Y29" s="6"/>
       <c r="Z29" s="6"/>
-      <c r="AA29" t="s">
+      <c r="AA29" s="6"/>
+      <c r="AB29" s="6"/>
+      <c r="AC29" t="s">
         <v>32</v>
       </c>
-      <c r="AB29" t="s">
+      <c r="AD29" t="s">
         <v>33</v>
       </c>
-      <c r="AJ29" s="10">
+      <c r="AL29" s="10">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:36" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="AJ30" s="10">
+    <row r="30" spans="1:38" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A30">
+        <v>5</v>
+      </c>
+      <c r="B30" t="str">
+        <f t="shared" si="0"/>
+        <v>high·$100·Y·001%</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="D30" t="s">
+        <v>82</v>
+      </c>
+      <c r="E30" s="15">
+        <f t="shared" ref="E30:E32" si="13">E26</f>
+        <v>100</v>
+      </c>
+      <c r="F30" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G30" s="33">
+        <v>0.01</v>
+      </c>
+      <c r="AL30" s="10">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="AJ31" s="10">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A31">
+        <v>5</v>
+      </c>
+      <c r="B31" t="str">
+        <f t="shared" si="0"/>
+        <v>high·$200·Y·001%</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="D31" t="s">
+        <v>82</v>
+      </c>
+      <c r="E31" s="15">
+        <f t="shared" si="13"/>
+        <v>200</v>
+      </c>
+      <c r="F31" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G31" s="33">
+        <v>0.01</v>
+      </c>
+      <c r="AL31" s="10">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.45">
-      <c r="AJ32" s="10">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A32">
+        <v>5</v>
+      </c>
+      <c r="B32" t="str">
+        <f t="shared" si="0"/>
+        <v>high·$300·Y·001%</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="D32" t="s">
+        <v>82</v>
+      </c>
+      <c r="E32" s="15">
+        <f t="shared" si="13"/>
+        <v>300</v>
+      </c>
+      <c r="F32" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G32" s="33">
+        <v>0.01</v>
+      </c>
+      <c r="AL32" s="10">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="7:36" x14ac:dyDescent="0.45">
-      <c r="AJ33" s="10">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A33">
+        <v>5</v>
+      </c>
+      <c r="B33" t="str">
+        <f t="shared" si="0"/>
+        <v>base·$000·N·001%</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="D33" t="s">
+        <v>114</v>
+      </c>
+      <c r="E33" s="15">
+        <v>0</v>
+      </c>
+      <c r="F33" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G33" s="33">
+        <v>0.01</v>
+      </c>
+      <c r="AL33" s="10">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="7:36" x14ac:dyDescent="0.45">
-      <c r="AJ34" s="10">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A34">
+        <v>5</v>
+      </c>
+      <c r="B34" t="str">
+        <f t="shared" si="0"/>
+        <v>base·$100·N·001%</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="D34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E34" s="15">
+        <v>100</v>
+      </c>
+      <c r="F34" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G34" s="33">
+        <v>0.01</v>
+      </c>
+      <c r="AL34" s="10">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="7:36" x14ac:dyDescent="0.45">
-      <c r="AJ35" s="10">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A35">
+        <v>5</v>
+      </c>
+      <c r="B35" t="str">
+        <f t="shared" si="0"/>
+        <v>base·$200·N·001%</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="D35" t="s">
+        <v>114</v>
+      </c>
+      <c r="E35" s="15">
+        <v>200</v>
+      </c>
+      <c r="F35" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G35" s="33">
+        <v>0.01</v>
+      </c>
+      <c r="AL35" s="10">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="7:36" x14ac:dyDescent="0.45">
-      <c r="G36" s="2" t="s">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A36">
+        <v>5</v>
+      </c>
+      <c r="B36" t="str">
+        <f t="shared" si="0"/>
+        <v>base·$300·N·001%</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="D36" t="s">
+        <v>114</v>
+      </c>
+      <c r="E36" s="15">
+        <v>300</v>
+      </c>
+      <c r="F36" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G36" s="33">
+        <v>0.01</v>
+      </c>
+      <c r="I36" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AJ36" s="10">
+      <c r="AL36" s="10">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="7:36" x14ac:dyDescent="0.45">
-      <c r="G37" t="s">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A37">
+        <v>5</v>
+      </c>
+      <c r="B37" t="str">
+        <f t="shared" si="0"/>
+        <v>high·$000·N·001%</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="D37" t="s">
+        <v>82</v>
+      </c>
+      <c r="E37" s="15">
+        <f>E33</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G37" s="33">
+        <v>0.01</v>
+      </c>
+      <c r="I37" t="s">
         <v>73</v>
       </c>
-      <c r="I37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!I$17,ar6_r10!$M$2:$M$999,Veda!$G37)</f>
-        <v>1</v>
-      </c>
-      <c r="J37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G37)</f>
+      <c r="K37" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
+        <v>1</v>
+      </c>
+      <c r="L37" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
         <v>1.1100000000000001</v>
       </c>
-      <c r="K37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G37)</f>
+      <c r="M37" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
         <v>1.21</v>
       </c>
-      <c r="L37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G37)</f>
+      <c r="N37" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
         <v>1.1599999999999999</v>
       </c>
-      <c r="M37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G37)</f>
+      <c r="O37" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
         <v>1.36</v>
       </c>
-      <c r="N37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G37)</f>
+      <c r="P37" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
         <v>1.4</v>
       </c>
-      <c r="O37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G37)</f>
+      <c r="Q37" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
         <v>1.44</v>
       </c>
-      <c r="AJ37" s="10">
+      <c r="AL37" s="10">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="7:36" x14ac:dyDescent="0.45">
-      <c r="G38" t="s">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A38">
+        <v>5</v>
+      </c>
+      <c r="B38" t="str">
+        <f t="shared" si="0"/>
+        <v>high·$100·N·001%</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="D38" t="s">
+        <v>82</v>
+      </c>
+      <c r="E38" s="15">
+        <f t="shared" ref="E38:E40" si="14">E34</f>
+        <v>100</v>
+      </c>
+      <c r="F38" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G38" s="33">
+        <v>0.01</v>
+      </c>
+      <c r="I38" t="s">
         <v>74</v>
       </c>
-      <c r="I38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!I$17,ar6_r10!$M$2:$M$999,Veda!$G38)</f>
-        <v>1</v>
-      </c>
-      <c r="J38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G38)</f>
+      <c r="K38" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
+        <v>1</v>
+      </c>
+      <c r="L38" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
         <v>1.07</v>
       </c>
-      <c r="K38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G38)</f>
+      <c r="M38" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
         <v>1.17</v>
       </c>
-      <c r="L38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G38)</f>
+      <c r="N38" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
         <v>1.21</v>
       </c>
-      <c r="M38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G38)</f>
+      <c r="O38" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
         <v>1.37</v>
       </c>
-      <c r="N38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G38)</f>
+      <c r="P38" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
         <v>1.33</v>
       </c>
-      <c r="O38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G38)</f>
+      <c r="Q38" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
         <v>1.52</v>
       </c>
-      <c r="AJ38" s="10">
+      <c r="AL38" s="10">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="7:36" x14ac:dyDescent="0.45">
-      <c r="G39" t="s">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A39">
+        <v>5</v>
+      </c>
+      <c r="B39" t="str">
+        <f t="shared" si="0"/>
+        <v>high·$200·N·001%</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="D39" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39" s="15">
+        <f t="shared" si="14"/>
+        <v>200</v>
+      </c>
+      <c r="F39" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G39" s="33">
+        <v>0.01</v>
+      </c>
+      <c r="I39" t="s">
         <v>75</v>
       </c>
-      <c r="I39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!I$17,ar6_r10!$M$2:$M$999,Veda!$G39)</f>
-        <v>1</v>
-      </c>
-      <c r="J39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G39)</f>
+      <c r="K39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
+        <v>1</v>
+      </c>
+      <c r="L39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
         <v>1.43</v>
       </c>
-      <c r="K39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G39)</f>
+      <c r="M39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
         <v>1.58</v>
       </c>
-      <c r="L39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G39)</f>
+      <c r="N39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
         <v>1.53</v>
       </c>
-      <c r="M39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G39)</f>
+      <c r="O39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
         <v>1.74</v>
       </c>
-      <c r="N39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G39)</f>
+      <c r="P39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
         <v>1.94</v>
       </c>
-      <c r="O39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G39)</f>
+      <c r="Q39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="AJ39" s="10">
+      <c r="AL39" s="10">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="7:36" x14ac:dyDescent="0.45">
-      <c r="G40" t="s">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A40">
+        <v>5</v>
+      </c>
+      <c r="B40" t="str">
+        <f t="shared" si="0"/>
+        <v>high·$300·N·001%</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="D40" t="s">
+        <v>82</v>
+      </c>
+      <c r="E40" s="15">
+        <f t="shared" si="14"/>
+        <v>300</v>
+      </c>
+      <c r="F40" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G40" s="33">
+        <v>0.01</v>
+      </c>
+      <c r="I40" t="s">
         <v>76</v>
       </c>
-      <c r="I40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!I$17,ar6_r10!$M$2:$M$999,Veda!$G40)</f>
-        <v>1</v>
-      </c>
-      <c r="J40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$G40)</f>
+      <c r="K40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
+        <v>1</v>
+      </c>
+      <c r="L40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
         <v>1.05</v>
       </c>
-      <c r="K40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G40)</f>
+      <c r="M40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
         <v>1.06</v>
       </c>
-      <c r="L40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G40)</f>
+      <c r="N40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
         <v>1.04</v>
       </c>
-      <c r="M40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G40)</f>
-        <v>1</v>
-      </c>
-      <c r="N40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G40)</f>
+      <c r="O40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
+        <v>1</v>
+      </c>
+      <c r="P40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
         <v>0.95</v>
       </c>
-      <c r="O40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$G$36,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G40)</f>
+      <c r="Q40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
         <v>0.93</v>
       </c>
-      <c r="AJ40" s="10">
+      <c r="AL40" s="10">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="7:36" x14ac:dyDescent="0.45">
-      <c r="AJ41" s="10">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="AL41" s="10">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="7:36" x14ac:dyDescent="0.45">
-      <c r="AJ42" s="10">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="AL42" s="10">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="7:36" x14ac:dyDescent="0.45">
-      <c r="G43" t="s">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="I43" t="s">
         <v>101</v>
       </c>
-      <c r="AJ43" s="10">
+      <c r="AL43" s="10">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="7:36" x14ac:dyDescent="0.45">
-      <c r="G44" t="s">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="I44" t="s">
         <v>13</v>
       </c>
-      <c r="H44" t="s">
+      <c r="J44" t="s">
         <v>86</v>
       </c>
-      <c r="I44">
+      <c r="K44">
         <v>2022</v>
       </c>
-      <c r="J44">
-        <f>J17</f>
+      <c r="L44">
+        <f>L17</f>
         <v>2025</v>
       </c>
-      <c r="K44">
-        <f t="shared" ref="K44:O44" si="12">K17</f>
+      <c r="M44">
+        <f t="shared" ref="M44:Q44" si="15">M17</f>
         <v>2030</v>
       </c>
-      <c r="L44">
-        <f t="shared" si="12"/>
+      <c r="N44">
+        <f t="shared" si="15"/>
         <v>2035</v>
       </c>
-      <c r="M44">
-        <f t="shared" si="12"/>
+      <c r="O44">
+        <f t="shared" si="15"/>
         <v>2040</v>
       </c>
-      <c r="N44">
-        <f t="shared" si="12"/>
+      <c r="P44">
+        <f t="shared" si="15"/>
         <v>2045</v>
       </c>
-      <c r="O44">
-        <f t="shared" si="12"/>
+      <c r="Q44">
+        <f t="shared" si="15"/>
         <v>2050</v>
       </c>
-      <c r="R44" t="s">
+      <c r="T44" t="s">
         <v>81</v>
       </c>
-      <c r="S44" t="s">
+      <c r="U44" t="s">
         <v>82</v>
       </c>
-      <c r="AJ44" s="10">
+      <c r="AL44" s="10">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="7:36" x14ac:dyDescent="0.45">
-      <c r="G45" t="s">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="I45" t="s">
         <v>77</v>
       </c>
-      <c r="H45" t="str">
-        <f>G45</f>
+      <c r="J45" t="str">
+        <f>I45</f>
         <v>Gas</v>
       </c>
-      <c r="I45">
-        <f t="shared" ref="I45:O48" si="13">AVERAGE($R45:$S45)*I37</f>
+      <c r="K45">
+        <f t="shared" ref="K45:Q48" si="16">AVERAGE($T45:$U45)*K37</f>
         <v>36</v>
       </c>
-      <c r="J45">
-        <f t="shared" si="13"/>
+      <c r="L45">
+        <f t="shared" si="16"/>
         <v>39.96</v>
       </c>
-      <c r="K45">
-        <f t="shared" si="13"/>
+      <c r="M45">
+        <f t="shared" si="16"/>
         <v>43.56</v>
       </c>
-      <c r="L45">
-        <f t="shared" si="13"/>
+      <c r="N45">
+        <f t="shared" si="16"/>
         <v>41.76</v>
       </c>
-      <c r="M45">
-        <f t="shared" si="13"/>
+      <c r="O45">
+        <f t="shared" si="16"/>
         <v>48.96</v>
       </c>
-      <c r="N45">
-        <f t="shared" si="13"/>
+      <c r="P45">
+        <f t="shared" si="16"/>
         <v>50.4</v>
       </c>
-      <c r="O45">
-        <f t="shared" si="13"/>
+      <c r="Q45">
+        <f t="shared" si="16"/>
         <v>51.839999999999996</v>
       </c>
-      <c r="R45">
-        <f>HLOOKUP($G45&amp;"_"&amp;R$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="T45">
+        <f>HLOOKUP($I45&amp;"_"&amp;T$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>30.9</v>
       </c>
-      <c r="S45">
-        <f>HLOOKUP($G45&amp;"_"&amp;S$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="U45">
+        <f>HLOOKUP($I45&amp;"_"&amp;U$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>41.1</v>
       </c>
-      <c r="AJ45" s="10">
+      <c r="AL45" s="10">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="7:36" x14ac:dyDescent="0.45">
-      <c r="G46" t="s">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="I46" t="s">
         <v>78</v>
       </c>
-      <c r="H46" t="str">
-        <f t="shared" ref="H46:H48" si="14">G46</f>
+      <c r="J46" t="str">
+        <f t="shared" ref="J46:J48" si="17">I46</f>
         <v>Coal</v>
       </c>
-      <c r="I46">
-        <f t="shared" si="13"/>
+      <c r="K46">
+        <f t="shared" si="16"/>
         <v>9.8000000000000007</v>
       </c>
-      <c r="J46">
-        <f t="shared" si="13"/>
+      <c r="L46">
+        <f t="shared" si="16"/>
         <v>10.486000000000001</v>
       </c>
-      <c r="K46">
-        <f t="shared" si="13"/>
+      <c r="M46">
+        <f t="shared" si="16"/>
         <v>11.465999999999999</v>
       </c>
-      <c r="L46">
-        <f t="shared" si="13"/>
+      <c r="N46">
+        <f t="shared" si="16"/>
         <v>11.858000000000001</v>
       </c>
-      <c r="M46">
-        <f t="shared" si="13"/>
+      <c r="O46">
+        <f t="shared" si="16"/>
         <v>13.426000000000002</v>
       </c>
-      <c r="N46">
-        <f t="shared" si="13"/>
+      <c r="P46">
+        <f t="shared" si="16"/>
         <v>13.034000000000002</v>
       </c>
-      <c r="O46">
-        <f t="shared" si="13"/>
+      <c r="Q46">
+        <f t="shared" si="16"/>
         <v>14.896000000000001</v>
       </c>
-      <c r="R46">
-        <f>HLOOKUP($G46&amp;"_"&amp;R$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="T46">
+        <f>HLOOKUP($I46&amp;"_"&amp;T$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>8.6</v>
       </c>
-      <c r="S46">
-        <f>HLOOKUP($G46&amp;"_"&amp;S$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="U46">
+        <f>HLOOKUP($I46&amp;"_"&amp;U$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>11</v>
       </c>
-      <c r="AJ46" s="10">
+      <c r="AL46" s="10">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="7:36" x14ac:dyDescent="0.45">
-      <c r="G47" t="s">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="I47" t="s">
         <v>79</v>
       </c>
-      <c r="H47" t="str">
-        <f t="shared" si="14"/>
+      <c r="J47" t="str">
+        <f t="shared" si="17"/>
         <v>Oil</v>
       </c>
-      <c r="I47">
-        <f t="shared" si="13"/>
+      <c r="K47">
+        <f t="shared" si="16"/>
         <v>50</v>
       </c>
-      <c r="J47">
-        <f t="shared" si="13"/>
+      <c r="L47">
+        <f t="shared" si="16"/>
         <v>71.5</v>
       </c>
-      <c r="K47">
-        <f t="shared" si="13"/>
+      <c r="M47">
+        <f t="shared" si="16"/>
         <v>79</v>
       </c>
-      <c r="L47">
-        <f t="shared" si="13"/>
+      <c r="N47">
+        <f t="shared" si="16"/>
         <v>76.5</v>
       </c>
-      <c r="M47">
-        <f t="shared" si="13"/>
+      <c r="O47">
+        <f t="shared" si="16"/>
         <v>87</v>
       </c>
-      <c r="N47">
-        <f t="shared" si="13"/>
+      <c r="P47">
+        <f t="shared" si="16"/>
         <v>97</v>
       </c>
-      <c r="O47">
-        <f t="shared" si="13"/>
+      <c r="Q47">
+        <f t="shared" si="16"/>
         <v>110.00000000000001</v>
       </c>
-      <c r="R47">
-        <f>HLOOKUP($G47&amp;"_"&amp;R$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="T47">
+        <f>HLOOKUP($I47&amp;"_"&amp;T$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>45</v>
       </c>
-      <c r="S47">
-        <f>HLOOKUP($G47&amp;"_"&amp;S$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="U47">
+        <f>HLOOKUP($I47&amp;"_"&amp;U$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>55</v>
       </c>
-      <c r="AJ47" s="10">
+      <c r="AL47" s="10">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="7:36" x14ac:dyDescent="0.45">
-      <c r="G48" t="s">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="I48" t="s">
         <v>80</v>
       </c>
-      <c r="H48" t="str">
-        <f t="shared" si="14"/>
+      <c r="J48" t="str">
+        <f t="shared" si="17"/>
         <v>Bioenergy</v>
       </c>
-      <c r="I48">
-        <f t="shared" si="13"/>
+      <c r="K48">
+        <f t="shared" si="16"/>
         <v>18.5</v>
       </c>
-      <c r="O48">
-        <f>VLOOKUP($H$14,$AK$9:$AM$15,3,FALSE)*I48</f>
+      <c r="Q48">
+        <f>VLOOKUP($J$14,$AM$9:$AO$15,3,FALSE)*K48</f>
         <v>55.5</v>
       </c>
-      <c r="R48">
-        <f>HLOOKUP($G48&amp;"_"&amp;R$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="T48">
+        <f>HLOOKUP($I48&amp;"_"&amp;T$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>15</v>
       </c>
-      <c r="S48">
-        <f>HLOOKUP($G48&amp;"_"&amp;S$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="U48">
+        <f>HLOOKUP($I48&amp;"_"&amp;U$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>22</v>
       </c>
-      <c r="AJ48" s="10">
+      <c r="AL48" s="10">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ49" s="10">
+    <row r="49" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL49" s="10">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ50" s="10">
+    <row r="50" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL50" s="10">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ51" s="10">
+    <row r="51" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL51" s="10">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ52" s="10">
+    <row r="52" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL52" s="10">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ53" s="10">
+    <row r="53" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL53" s="10">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ54" s="10">
+    <row r="54" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL54" s="10">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ55" s="10">
+    <row r="55" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL55" s="10">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ56" s="10">
+    <row r="56" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL56" s="10">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ57" s="10">
+    <row r="57" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL57" s="10">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ58" s="10">
+    <row r="58" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL58" s="10">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ59" s="10">
+    <row r="59" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL59" s="10">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ60" s="10">
+    <row r="60" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL60" s="10">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ61" s="10">
+    <row r="61" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL61" s="10">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ62" s="10">
+    <row r="62" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL62" s="10">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ63" s="10">
+    <row r="63" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL63" s="10">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ64" s="10">
+    <row r="64" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL64" s="10">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ65" s="10">
+    <row r="65" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL65" s="10">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ66" s="10">
+    <row r="66" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL66" s="10">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ67" s="10">
+    <row r="67" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL67" s="10">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ68" s="10">
+    <row r="68" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL68" s="10">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ69" s="10">
+    <row r="69" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL69" s="10">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ70" s="10">
+    <row r="70" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL70" s="10">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ71" s="10">
+    <row r="71" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL71" s="10">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ72" s="10">
+    <row r="72" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL72" s="10">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ73" s="10">
+    <row r="73" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL73" s="10">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ74" s="10">
+    <row r="74" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL74" s="10">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ75" s="10">
+    <row r="75" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL75" s="10">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ76" s="10">
+    <row r="76" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL76" s="10">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ77" s="10">
+    <row r="77" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL77" s="10">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="36:36" x14ac:dyDescent="0.45">
-      <c r="AJ78" s="10">
+    <row r="78" spans="38:38" x14ac:dyDescent="0.45">
+      <c r="AL78" s="10">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A82" s="12" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A83" s="16" t="s">
         <v>29</v>
       </c>
@@ -7824,11 +8532,13 @@
       <c r="E83" s="16">
         <v>2040</v>
       </c>
-      <c r="F83" s="16" t="s">
+      <c r="F83" s="16"/>
+      <c r="G83" s="16"/>
+      <c r="H83" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A84" s="17" t="s">
         <v>34</v>
       </c>
@@ -7844,11 +8554,13 @@
       <c r="E84" s="18">
         <v>1.881</v>
       </c>
-      <c r="F84" s="17" t="s">
+      <c r="F84" s="18"/>
+      <c r="G84" s="18"/>
+      <c r="H84" s="17" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A85" s="19" t="s">
         <v>31</v>
       </c>
@@ -7864,7 +8576,9 @@
       <c r="E85" s="20">
         <v>3.3</v>
       </c>
-      <c r="F85" s="19" t="s">
+      <c r="F85" s="20"/>
+      <c r="G85" s="20"/>
+      <c r="H85" s="19" t="s">
         <v>119</v>
       </c>
     </row>
@@ -7877,6 +8591,179 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CD5270F-E5C6-4B02-8A48-7D871D6014E5}">
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" t="str">
+        <f>Veda!$F$5</f>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <f>Veda!$G$5</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C3" t="str">
+        <f>IF($A$1="Y","DEF active","~TFM_UPD")</f>
+        <v>DEF active</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C8" t="str">
+        <f>IF($A$1="Y","DEF active","~TFM_INS: limtype=LO")</f>
+        <v>DEF active</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" t="s">
+        <v>128</v>
+      </c>
+      <c r="G9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>-13</v>
+      </c>
+      <c r="G10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C11" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>-13</v>
+      </c>
+      <c r="G11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C14" t="str">
+        <f>IF($A$1="Y","DEF active","~TFM_UPD")</f>
+        <v>DEF active</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>141</v>
+      </c>
+      <c r="E15" t="s">
+        <v>138</v>
+      </c>
+      <c r="F15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C16" t="s">
+        <v>140</v>
+      </c>
+      <c r="D16" t="s">
+        <v>139</v>
+      </c>
+      <c r="E16" t="s">
+        <v>139</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C20" t="str">
+        <f>IF($A$2=1,"Tx cost 100%","~TFM_UPD")</f>
+        <v>Tx cost 100%</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C22" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" t="str">
+        <f>"*"&amp;A2</f>
+        <v>*1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>145</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3D3AADB-9A32-40E9-8F4D-C4BF39898AB4}">
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -7927,7 +8814,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B11">
         <v>30.9</v>
@@ -7954,7 +8841,7 @@
         <v>22</v>
       </c>
       <c r="J11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -7963,7 +8850,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -8014,7 +8901,7 @@
         <v>43</v>
       </c>
       <c r="J10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K10" t="s">
         <v>116</v>
@@ -8022,7 +8909,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B11">
         <v>2000</v>
@@ -8057,7 +8944,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12">
         <v>2001</v>
@@ -8092,7 +8979,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B13">
         <v>2002</v>
@@ -8127,7 +9014,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B14">
         <v>2003</v>
@@ -8162,7 +9049,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B15">
         <v>2004</v>
@@ -8197,7 +9084,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B16">
         <v>2005</v>
@@ -8232,7 +9119,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B17">
         <v>2006</v>
@@ -8267,7 +9154,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B18">
         <v>2007</v>
@@ -8302,7 +9189,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B19">
         <v>2008</v>
@@ -8337,7 +9224,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B20">
         <v>2009</v>
@@ -8372,7 +9259,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B21">
         <v>2010</v>
@@ -8407,7 +9294,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B22">
         <v>2011</v>
@@ -8442,7 +9329,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B23">
         <v>2012</v>
@@ -8477,7 +9364,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B24">
         <v>2013</v>
@@ -8512,7 +9399,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B25">
         <v>2014</v>
@@ -8547,7 +9434,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B26">
         <v>2015</v>
@@ -8582,7 +9469,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B27">
         <v>2016</v>
@@ -8617,7 +9504,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B28">
         <v>2017</v>
@@ -8652,7 +9539,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B29">
         <v>2018</v>
@@ -8687,7 +9574,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B30">
         <v>2019</v>
@@ -8722,7 +9609,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B31">
         <v>2020</v>
@@ -8757,7 +9644,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B32">
         <v>2021</v>
@@ -8792,7 +9679,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B33">
         <v>2022</v>
@@ -8831,7 +9718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M395"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -8896,7 +9783,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C11">
         <v>2020</v>
@@ -8937,7 +9824,7 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C12">
         <v>2025</v>
@@ -8978,7 +9865,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13">
         <v>2030</v>
@@ -9019,7 +9906,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C14">
         <v>2035</v>
@@ -9060,7 +9947,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C15">
         <v>2040</v>
@@ -9101,7 +9988,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C16">
         <v>2045</v>
@@ -9142,7 +10029,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C17">
         <v>2050</v>
@@ -9183,7 +10070,7 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C18">
         <v>2020</v>
@@ -9224,7 +10111,7 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C19">
         <v>2025</v>
@@ -9265,7 +10152,7 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C20">
         <v>2030</v>
@@ -9306,7 +10193,7 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C21">
         <v>2035</v>
@@ -9347,7 +10234,7 @@
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C22">
         <v>2040</v>
@@ -9388,7 +10275,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C23">
         <v>2045</v>
@@ -9429,7 +10316,7 @@
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C24">
         <v>2050</v>
@@ -9470,7 +10357,7 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C25">
         <v>2020</v>
@@ -9511,7 +10398,7 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C26">
         <v>2025</v>
@@ -9552,7 +10439,7 @@
         <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C27">
         <v>2030</v>
@@ -9593,7 +10480,7 @@
         <v>5</v>
       </c>
       <c r="B28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C28">
         <v>2035</v>
@@ -9634,7 +10521,7 @@
         <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C29">
         <v>2040</v>
@@ -9675,7 +10562,7 @@
         <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C30">
         <v>2045</v>
@@ -9716,7 +10603,7 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C31">
         <v>2050</v>
@@ -9757,7 +10644,7 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C32">
         <v>2020</v>
@@ -9798,7 +10685,7 @@
         <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C33">
         <v>2025</v>
@@ -9839,7 +10726,7 @@
         <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C34">
         <v>2030</v>
@@ -9880,7 +10767,7 @@
         <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C35">
         <v>2035</v>
@@ -9921,7 +10808,7 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C36">
         <v>2040</v>
@@ -9962,7 +10849,7 @@
         <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C37">
         <v>2045</v>
@@ -10003,7 +10890,7 @@
         <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C38">
         <v>2050</v>
@@ -10044,7 +10931,7 @@
         <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C39">
         <v>2020</v>
@@ -10085,7 +10972,7 @@
         <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C40">
         <v>2025</v>
@@ -10126,7 +11013,7 @@
         <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C41">
         <v>2030</v>
@@ -10167,7 +11054,7 @@
         <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C42">
         <v>2035</v>
@@ -10208,7 +11095,7 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C43">
         <v>2040</v>
@@ -10249,7 +11136,7 @@
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C44">
         <v>2045</v>
@@ -10290,7 +11177,7 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C45">
         <v>2050</v>
@@ -10331,7 +11218,7 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C46">
         <v>2020</v>
@@ -10372,7 +11259,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C47">
         <v>2025</v>
@@ -10413,7 +11300,7 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C48">
         <v>2030</v>
@@ -10454,7 +11341,7 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C49">
         <v>2035</v>
@@ -10495,7 +11382,7 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C50">
         <v>2040</v>
@@ -10536,7 +11423,7 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C51">
         <v>2045</v>
@@ -10577,7 +11464,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C52">
         <v>2050</v>
@@ -10618,7 +11505,7 @@
         <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C53">
         <v>2020</v>
@@ -10659,7 +11546,7 @@
         <v>2</v>
       </c>
       <c r="B54" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C54">
         <v>2025</v>
@@ -10700,7 +11587,7 @@
         <v>2</v>
       </c>
       <c r="B55" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C55">
         <v>2030</v>
@@ -10741,7 +11628,7 @@
         <v>2</v>
       </c>
       <c r="B56" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C56">
         <v>2035</v>
@@ -10782,7 +11669,7 @@
         <v>2</v>
       </c>
       <c r="B57" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C57">
         <v>2040</v>
@@ -10823,7 +11710,7 @@
         <v>2</v>
       </c>
       <c r="B58" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C58">
         <v>2045</v>
@@ -10864,7 +11751,7 @@
         <v>2</v>
       </c>
       <c r="B59" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C59">
         <v>2050</v>
@@ -10905,7 +11792,7 @@
         <v>5</v>
       </c>
       <c r="B60" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C60">
         <v>2020</v>
@@ -10946,7 +11833,7 @@
         <v>5</v>
       </c>
       <c r="B61" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C61">
         <v>2025</v>
@@ -10987,7 +11874,7 @@
         <v>5</v>
       </c>
       <c r="B62" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C62">
         <v>2030</v>
@@ -11028,7 +11915,7 @@
         <v>5</v>
       </c>
       <c r="B63" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C63">
         <v>2035</v>
@@ -11069,7 +11956,7 @@
         <v>5</v>
       </c>
       <c r="B64" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C64">
         <v>2040</v>
@@ -11110,7 +11997,7 @@
         <v>5</v>
       </c>
       <c r="B65" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C65">
         <v>2045</v>
@@ -11151,7 +12038,7 @@
         <v>5</v>
       </c>
       <c r="B66" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C66">
         <v>2050</v>
@@ -11192,7 +12079,7 @@
         <v>7</v>
       </c>
       <c r="B67" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C67">
         <v>2020</v>
@@ -11233,7 +12120,7 @@
         <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C68">
         <v>2025</v>
@@ -11274,7 +12161,7 @@
         <v>7</v>
       </c>
       <c r="B69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C69">
         <v>2030</v>
@@ -11315,7 +12202,7 @@
         <v>7</v>
       </c>
       <c r="B70" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C70">
         <v>2035</v>
@@ -11356,7 +12243,7 @@
         <v>7</v>
       </c>
       <c r="B71" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C71">
         <v>2040</v>
@@ -11397,7 +12284,7 @@
         <v>7</v>
       </c>
       <c r="B72" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C72">
         <v>2045</v>
@@ -11438,7 +12325,7 @@
         <v>7</v>
       </c>
       <c r="B73" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C73">
         <v>2050</v>
@@ -11479,7 +12366,7 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C74">
         <v>2020</v>
@@ -11520,7 +12407,7 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C75">
         <v>2025</v>
@@ -11561,7 +12448,7 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C76">
         <v>2030</v>
@@ -11602,7 +12489,7 @@
         <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C77">
         <v>2035</v>
@@ -11643,7 +12530,7 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C78">
         <v>2040</v>
@@ -11684,7 +12571,7 @@
         <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C79">
         <v>2045</v>
@@ -11725,7 +12612,7 @@
         <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C80">
         <v>2050</v>
@@ -11766,7 +12653,7 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C81">
         <v>2020</v>
@@ -11807,7 +12694,7 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C82">
         <v>2025</v>
@@ -11848,7 +12735,7 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C83">
         <v>2030</v>
@@ -11889,7 +12776,7 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C84">
         <v>2035</v>
@@ -11930,7 +12817,7 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C85">
         <v>2040</v>
@@ -11971,7 +12858,7 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C86">
         <v>2045</v>
@@ -12012,7 +12899,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C87">
         <v>2050</v>
@@ -12053,7 +12940,7 @@
         <v>2</v>
       </c>
       <c r="B88" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C88">
         <v>2020</v>
@@ -12094,7 +12981,7 @@
         <v>2</v>
       </c>
       <c r="B89" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C89">
         <v>2025</v>
@@ -12135,7 +13022,7 @@
         <v>2</v>
       </c>
       <c r="B90" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C90">
         <v>2030</v>
@@ -12176,7 +13063,7 @@
         <v>2</v>
       </c>
       <c r="B91" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C91">
         <v>2035</v>
@@ -12217,7 +13104,7 @@
         <v>2</v>
       </c>
       <c r="B92" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C92">
         <v>2040</v>
@@ -12258,7 +13145,7 @@
         <v>2</v>
       </c>
       <c r="B93" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C93">
         <v>2045</v>
@@ -12299,7 +13186,7 @@
         <v>2</v>
       </c>
       <c r="B94" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C94">
         <v>2050</v>
@@ -12340,7 +13227,7 @@
         <v>5</v>
       </c>
       <c r="B95" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C95">
         <v>2020</v>
@@ -12381,7 +13268,7 @@
         <v>5</v>
       </c>
       <c r="B96" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C96">
         <v>2025</v>
@@ -12422,7 +13309,7 @@
         <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C97">
         <v>2030</v>
@@ -12463,7 +13350,7 @@
         <v>5</v>
       </c>
       <c r="B98" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C98">
         <v>2035</v>
@@ -12504,7 +13391,7 @@
         <v>5</v>
       </c>
       <c r="B99" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C99">
         <v>2040</v>
@@ -12545,7 +13432,7 @@
         <v>5</v>
       </c>
       <c r="B100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C100">
         <v>2045</v>
@@ -12586,7 +13473,7 @@
         <v>5</v>
       </c>
       <c r="B101" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C101">
         <v>2050</v>
@@ -12627,7 +13514,7 @@
         <v>7</v>
       </c>
       <c r="B102" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C102">
         <v>2020</v>
@@ -12668,7 +13555,7 @@
         <v>7</v>
       </c>
       <c r="B103" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C103">
         <v>2025</v>
@@ -12709,7 +13596,7 @@
         <v>7</v>
       </c>
       <c r="B104" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C104">
         <v>2030</v>
@@ -12750,7 +13637,7 @@
         <v>7</v>
       </c>
       <c r="B105" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C105">
         <v>2035</v>
@@ -12791,7 +13678,7 @@
         <v>7</v>
       </c>
       <c r="B106" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C106">
         <v>2040</v>
@@ -12832,7 +13719,7 @@
         <v>7</v>
       </c>
       <c r="B107" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C107">
         <v>2045</v>
@@ -12873,7 +13760,7 @@
         <v>7</v>
       </c>
       <c r="B108" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C108">
         <v>2050</v>
@@ -12914,7 +13801,7 @@
         <v>9</v>
       </c>
       <c r="B109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C109">
         <v>2020</v>
@@ -12955,7 +13842,7 @@
         <v>9</v>
       </c>
       <c r="B110" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C110">
         <v>2025</v>
@@ -12996,7 +13883,7 @@
         <v>9</v>
       </c>
       <c r="B111" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C111">
         <v>2030</v>
@@ -13037,7 +13924,7 @@
         <v>9</v>
       </c>
       <c r="B112" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C112">
         <v>2035</v>
@@ -13078,7 +13965,7 @@
         <v>9</v>
       </c>
       <c r="B113" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C113">
         <v>2040</v>
@@ -13119,7 +14006,7 @@
         <v>9</v>
       </c>
       <c r="B114" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C114">
         <v>2045</v>
@@ -13160,7 +14047,7 @@
         <v>9</v>
       </c>
       <c r="B115" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C115">
         <v>2050</v>
@@ -13201,7 +14088,7 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C116">
         <v>2020</v>
@@ -13242,7 +14129,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C117">
         <v>2025</v>
@@ -13283,7 +14170,7 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C118">
         <v>2030</v>
@@ -13324,7 +14211,7 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C119">
         <v>2035</v>
@@ -13365,7 +14252,7 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C120">
         <v>2040</v>
@@ -13406,7 +14293,7 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C121">
         <v>2045</v>
@@ -13447,7 +14334,7 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C122">
         <v>2050</v>
@@ -13488,7 +14375,7 @@
         <v>2</v>
       </c>
       <c r="B123" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C123">
         <v>2020</v>
@@ -13529,7 +14416,7 @@
         <v>2</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C124">
         <v>2025</v>
@@ -13570,7 +14457,7 @@
         <v>2</v>
       </c>
       <c r="B125" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C125">
         <v>2030</v>
@@ -13611,7 +14498,7 @@
         <v>2</v>
       </c>
       <c r="B126" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C126">
         <v>2035</v>
@@ -13652,7 +14539,7 @@
         <v>2</v>
       </c>
       <c r="B127" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C127">
         <v>2040</v>
@@ -13693,7 +14580,7 @@
         <v>2</v>
       </c>
       <c r="B128" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C128">
         <v>2045</v>
@@ -13734,7 +14621,7 @@
         <v>2</v>
       </c>
       <c r="B129" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C129">
         <v>2050</v>
@@ -13775,7 +14662,7 @@
         <v>5</v>
       </c>
       <c r="B130" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C130">
         <v>2020</v>
@@ -13816,7 +14703,7 @@
         <v>5</v>
       </c>
       <c r="B131" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C131">
         <v>2025</v>
@@ -13857,7 +14744,7 @@
         <v>5</v>
       </c>
       <c r="B132" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C132">
         <v>2030</v>
@@ -13898,7 +14785,7 @@
         <v>5</v>
       </c>
       <c r="B133" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C133">
         <v>2035</v>
@@ -13939,7 +14826,7 @@
         <v>5</v>
       </c>
       <c r="B134" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C134">
         <v>2040</v>
@@ -13980,7 +14867,7 @@
         <v>5</v>
       </c>
       <c r="B135" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C135">
         <v>2045</v>
@@ -14021,7 +14908,7 @@
         <v>5</v>
       </c>
       <c r="B136" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C136">
         <v>2050</v>
@@ -14062,7 +14949,7 @@
         <v>7</v>
       </c>
       <c r="B137" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C137">
         <v>2020</v>
@@ -14103,7 +14990,7 @@
         <v>7</v>
       </c>
       <c r="B138" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C138">
         <v>2025</v>
@@ -14144,7 +15031,7 @@
         <v>7</v>
       </c>
       <c r="B139" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C139">
         <v>2030</v>
@@ -14185,7 +15072,7 @@
         <v>7</v>
       </c>
       <c r="B140" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C140">
         <v>2035</v>
@@ -14226,7 +15113,7 @@
         <v>7</v>
       </c>
       <c r="B141" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C141">
         <v>2040</v>
@@ -14267,7 +15154,7 @@
         <v>7</v>
       </c>
       <c r="B142" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C142">
         <v>2045</v>
@@ -14308,7 +15195,7 @@
         <v>7</v>
       </c>
       <c r="B143" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C143">
         <v>2050</v>
@@ -14349,7 +15236,7 @@
         <v>9</v>
       </c>
       <c r="B144" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C144">
         <v>2020</v>
@@ -14390,7 +15277,7 @@
         <v>9</v>
       </c>
       <c r="B145" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C145">
         <v>2025</v>
@@ -14431,7 +15318,7 @@
         <v>9</v>
       </c>
       <c r="B146" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C146">
         <v>2030</v>
@@ -14472,7 +15359,7 @@
         <v>9</v>
       </c>
       <c r="B147" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C147">
         <v>2035</v>
@@ -14513,7 +15400,7 @@
         <v>9</v>
       </c>
       <c r="B148" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C148">
         <v>2040</v>
@@ -14554,7 +15441,7 @@
         <v>9</v>
       </c>
       <c r="B149" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C149">
         <v>2045</v>
@@ -14595,7 +15482,7 @@
         <v>9</v>
       </c>
       <c r="B150" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C150">
         <v>2050</v>
@@ -14636,7 +15523,7 @@
         <v>0</v>
       </c>
       <c r="B151" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C151">
         <v>2020</v>
@@ -14677,7 +15564,7 @@
         <v>0</v>
       </c>
       <c r="B152" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C152">
         <v>2025</v>
@@ -14718,7 +15605,7 @@
         <v>0</v>
       </c>
       <c r="B153" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C153">
         <v>2030</v>
@@ -14759,7 +15646,7 @@
         <v>0</v>
       </c>
       <c r="B154" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C154">
         <v>2035</v>
@@ -14800,7 +15687,7 @@
         <v>0</v>
       </c>
       <c r="B155" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C155">
         <v>2040</v>
@@ -14841,7 +15728,7 @@
         <v>0</v>
       </c>
       <c r="B156" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C156">
         <v>2045</v>
@@ -14882,7 +15769,7 @@
         <v>0</v>
       </c>
       <c r="B157" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C157">
         <v>2050</v>
@@ -14923,7 +15810,7 @@
         <v>2</v>
       </c>
       <c r="B158" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C158">
         <v>2020</v>
@@ -14964,7 +15851,7 @@
         <v>2</v>
       </c>
       <c r="B159" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C159">
         <v>2025</v>
@@ -15005,7 +15892,7 @@
         <v>2</v>
       </c>
       <c r="B160" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C160">
         <v>2030</v>
@@ -15046,7 +15933,7 @@
         <v>2</v>
       </c>
       <c r="B161" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C161">
         <v>2035</v>
@@ -15087,7 +15974,7 @@
         <v>2</v>
       </c>
       <c r="B162" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C162">
         <v>2040</v>
@@ -15128,7 +16015,7 @@
         <v>2</v>
       </c>
       <c r="B163" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C163">
         <v>2045</v>
@@ -15169,7 +16056,7 @@
         <v>2</v>
       </c>
       <c r="B164" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C164">
         <v>2050</v>
@@ -15210,7 +16097,7 @@
         <v>5</v>
       </c>
       <c r="B165" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C165">
         <v>2020</v>
@@ -15251,7 +16138,7 @@
         <v>5</v>
       </c>
       <c r="B166" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C166">
         <v>2025</v>
@@ -15292,7 +16179,7 @@
         <v>5</v>
       </c>
       <c r="B167" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C167">
         <v>2030</v>
@@ -15333,7 +16220,7 @@
         <v>5</v>
       </c>
       <c r="B168" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C168">
         <v>2035</v>
@@ -15374,7 +16261,7 @@
         <v>5</v>
       </c>
       <c r="B169" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C169">
         <v>2040</v>
@@ -15415,7 +16302,7 @@
         <v>5</v>
       </c>
       <c r="B170" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C170">
         <v>2045</v>
@@ -15456,7 +16343,7 @@
         <v>5</v>
       </c>
       <c r="B171" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C171">
         <v>2050</v>
@@ -15497,7 +16384,7 @@
         <v>7</v>
       </c>
       <c r="B172" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C172">
         <v>2020</v>
@@ -15538,7 +16425,7 @@
         <v>7</v>
       </c>
       <c r="B173" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C173">
         <v>2025</v>
@@ -15579,7 +16466,7 @@
         <v>7</v>
       </c>
       <c r="B174" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C174">
         <v>2030</v>
@@ -15620,7 +16507,7 @@
         <v>7</v>
       </c>
       <c r="B175" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C175">
         <v>2035</v>
@@ -15661,7 +16548,7 @@
         <v>7</v>
       </c>
       <c r="B176" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C176">
         <v>2040</v>
@@ -15702,7 +16589,7 @@
         <v>7</v>
       </c>
       <c r="B177" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C177">
         <v>2045</v>
@@ -15743,7 +16630,7 @@
         <v>7</v>
       </c>
       <c r="B178" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C178">
         <v>2050</v>
@@ -15784,7 +16671,7 @@
         <v>9</v>
       </c>
       <c r="B179" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C179">
         <v>2020</v>
@@ -15825,7 +16712,7 @@
         <v>9</v>
       </c>
       <c r="B180" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C180">
         <v>2025</v>
@@ -15866,7 +16753,7 @@
         <v>9</v>
       </c>
       <c r="B181" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C181">
         <v>2030</v>
@@ -15907,7 +16794,7 @@
         <v>9</v>
       </c>
       <c r="B182" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C182">
         <v>2035</v>
@@ -15948,7 +16835,7 @@
         <v>9</v>
       </c>
       <c r="B183" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C183">
         <v>2040</v>
@@ -15989,7 +16876,7 @@
         <v>9</v>
       </c>
       <c r="B184" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C184">
         <v>2045</v>
@@ -16030,7 +16917,7 @@
         <v>9</v>
       </c>
       <c r="B185" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C185">
         <v>2050</v>
@@ -16071,7 +16958,7 @@
         <v>0</v>
       </c>
       <c r="B186" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C186">
         <v>2020</v>
@@ -16112,7 +16999,7 @@
         <v>0</v>
       </c>
       <c r="B187" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C187">
         <v>2025</v>
@@ -16153,7 +17040,7 @@
         <v>0</v>
       </c>
       <c r="B188" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C188">
         <v>2030</v>
@@ -16194,7 +17081,7 @@
         <v>0</v>
       </c>
       <c r="B189" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C189">
         <v>2035</v>
@@ -16235,7 +17122,7 @@
         <v>0</v>
       </c>
       <c r="B190" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C190">
         <v>2040</v>
@@ -16276,7 +17163,7 @@
         <v>0</v>
       </c>
       <c r="B191" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C191">
         <v>2045</v>
@@ -16317,7 +17204,7 @@
         <v>0</v>
       </c>
       <c r="B192" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C192">
         <v>2050</v>
@@ -16358,7 +17245,7 @@
         <v>2</v>
       </c>
       <c r="B193" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C193">
         <v>2020</v>
@@ -16399,7 +17286,7 @@
         <v>2</v>
       </c>
       <c r="B194" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C194">
         <v>2025</v>
@@ -16440,7 +17327,7 @@
         <v>2</v>
       </c>
       <c r="B195" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C195">
         <v>2030</v>
@@ -16481,7 +17368,7 @@
         <v>2</v>
       </c>
       <c r="B196" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C196">
         <v>2035</v>
@@ -16522,7 +17409,7 @@
         <v>2</v>
       </c>
       <c r="B197" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C197">
         <v>2040</v>
@@ -16563,7 +17450,7 @@
         <v>2</v>
       </c>
       <c r="B198" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C198">
         <v>2045</v>
@@ -16604,7 +17491,7 @@
         <v>2</v>
       </c>
       <c r="B199" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C199">
         <v>2050</v>
@@ -16645,7 +17532,7 @@
         <v>5</v>
       </c>
       <c r="B200" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C200">
         <v>2020</v>
@@ -16686,7 +17573,7 @@
         <v>5</v>
       </c>
       <c r="B201" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C201">
         <v>2025</v>
@@ -16727,7 +17614,7 @@
         <v>5</v>
       </c>
       <c r="B202" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C202">
         <v>2030</v>
@@ -16768,7 +17655,7 @@
         <v>5</v>
       </c>
       <c r="B203" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C203">
         <v>2035</v>
@@ -16809,7 +17696,7 @@
         <v>5</v>
       </c>
       <c r="B204" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C204">
         <v>2040</v>
@@ -16850,7 +17737,7 @@
         <v>5</v>
       </c>
       <c r="B205" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C205">
         <v>2045</v>
@@ -16891,7 +17778,7 @@
         <v>5</v>
       </c>
       <c r="B206" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C206">
         <v>2050</v>
@@ -16932,7 +17819,7 @@
         <v>7</v>
       </c>
       <c r="B207" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C207">
         <v>2020</v>
@@ -16973,7 +17860,7 @@
         <v>7</v>
       </c>
       <c r="B208" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C208">
         <v>2025</v>
@@ -17014,7 +17901,7 @@
         <v>7</v>
       </c>
       <c r="B209" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C209">
         <v>2030</v>
@@ -17055,7 +17942,7 @@
         <v>7</v>
       </c>
       <c r="B210" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C210">
         <v>2035</v>
@@ -17096,7 +17983,7 @@
         <v>7</v>
       </c>
       <c r="B211" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C211">
         <v>2040</v>
@@ -17137,7 +18024,7 @@
         <v>7</v>
       </c>
       <c r="B212" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C212">
         <v>2045</v>
@@ -17178,7 +18065,7 @@
         <v>7</v>
       </c>
       <c r="B213" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C213">
         <v>2050</v>
@@ -17219,7 +18106,7 @@
         <v>9</v>
       </c>
       <c r="B214" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C214">
         <v>2020</v>
@@ -17260,7 +18147,7 @@
         <v>9</v>
       </c>
       <c r="B215" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C215">
         <v>2025</v>
@@ -17301,7 +18188,7 @@
         <v>9</v>
       </c>
       <c r="B216" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C216">
         <v>2030</v>
@@ -17342,7 +18229,7 @@
         <v>9</v>
       </c>
       <c r="B217" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C217">
         <v>2035</v>
@@ -17383,7 +18270,7 @@
         <v>9</v>
       </c>
       <c r="B218" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C218">
         <v>2040</v>
@@ -17424,7 +18311,7 @@
         <v>9</v>
       </c>
       <c r="B219" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C219">
         <v>2045</v>
@@ -17465,7 +18352,7 @@
         <v>9</v>
       </c>
       <c r="B220" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C220">
         <v>2050</v>
@@ -17506,7 +18393,7 @@
         <v>0</v>
       </c>
       <c r="B221" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C221">
         <v>2020</v>
@@ -17547,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="B222" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C222">
         <v>2025</v>
@@ -17588,7 +18475,7 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C223">
         <v>2030</v>
@@ -17629,7 +18516,7 @@
         <v>0</v>
       </c>
       <c r="B224" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C224">
         <v>2035</v>
@@ -17670,7 +18557,7 @@
         <v>0</v>
       </c>
       <c r="B225" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C225">
         <v>2040</v>
@@ -17711,7 +18598,7 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C226">
         <v>2045</v>
@@ -17752,7 +18639,7 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C227">
         <v>2050</v>
@@ -17793,7 +18680,7 @@
         <v>2</v>
       </c>
       <c r="B228" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C228">
         <v>2020</v>
@@ -17834,7 +18721,7 @@
         <v>2</v>
       </c>
       <c r="B229" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C229">
         <v>2025</v>
@@ -17875,7 +18762,7 @@
         <v>2</v>
       </c>
       <c r="B230" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C230">
         <v>2030</v>
@@ -17916,7 +18803,7 @@
         <v>2</v>
       </c>
       <c r="B231" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C231">
         <v>2035</v>
@@ -17957,7 +18844,7 @@
         <v>2</v>
       </c>
       <c r="B232" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C232">
         <v>2040</v>
@@ -17998,7 +18885,7 @@
         <v>2</v>
       </c>
       <c r="B233" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C233">
         <v>2045</v>
@@ -18039,7 +18926,7 @@
         <v>2</v>
       </c>
       <c r="B234" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C234">
         <v>2050</v>
@@ -18080,7 +18967,7 @@
         <v>5</v>
       </c>
       <c r="B235" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C235">
         <v>2020</v>
@@ -18121,7 +19008,7 @@
         <v>5</v>
       </c>
       <c r="B236" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C236">
         <v>2025</v>
@@ -18162,7 +19049,7 @@
         <v>5</v>
       </c>
       <c r="B237" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C237">
         <v>2030</v>
@@ -18203,7 +19090,7 @@
         <v>5</v>
       </c>
       <c r="B238" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C238">
         <v>2035</v>
@@ -18244,7 +19131,7 @@
         <v>5</v>
       </c>
       <c r="B239" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C239">
         <v>2040</v>
@@ -18285,7 +19172,7 @@
         <v>5</v>
       </c>
       <c r="B240" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C240">
         <v>2045</v>
@@ -18326,7 +19213,7 @@
         <v>5</v>
       </c>
       <c r="B241" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C241">
         <v>2050</v>
@@ -18367,7 +19254,7 @@
         <v>7</v>
       </c>
       <c r="B242" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C242">
         <v>2020</v>
@@ -18408,7 +19295,7 @@
         <v>7</v>
       </c>
       <c r="B243" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C243">
         <v>2025</v>
@@ -18449,7 +19336,7 @@
         <v>7</v>
       </c>
       <c r="B244" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C244">
         <v>2030</v>
@@ -18490,7 +19377,7 @@
         <v>7</v>
       </c>
       <c r="B245" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C245">
         <v>2035</v>
@@ -18531,7 +19418,7 @@
         <v>7</v>
       </c>
       <c r="B246" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C246">
         <v>2040</v>
@@ -18572,7 +19459,7 @@
         <v>7</v>
       </c>
       <c r="B247" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C247">
         <v>2045</v>
@@ -18613,7 +19500,7 @@
         <v>7</v>
       </c>
       <c r="B248" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C248">
         <v>2050</v>
@@ -18654,7 +19541,7 @@
         <v>9</v>
       </c>
       <c r="B249" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C249">
         <v>2020</v>
@@ -18695,7 +19582,7 @@
         <v>9</v>
       </c>
       <c r="B250" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C250">
         <v>2025</v>
@@ -18736,7 +19623,7 @@
         <v>9</v>
       </c>
       <c r="B251" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C251">
         <v>2030</v>
@@ -18777,7 +19664,7 @@
         <v>9</v>
       </c>
       <c r="B252" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C252">
         <v>2035</v>
@@ -18818,7 +19705,7 @@
         <v>9</v>
       </c>
       <c r="B253" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C253">
         <v>2040</v>
@@ -18859,7 +19746,7 @@
         <v>9</v>
       </c>
       <c r="B254" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C254">
         <v>2045</v>
@@ -18900,7 +19787,7 @@
         <v>9</v>
       </c>
       <c r="B255" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C255">
         <v>2050</v>
@@ -18941,7 +19828,7 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C256">
         <v>2020</v>
@@ -18982,7 +19869,7 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C257">
         <v>2025</v>
@@ -19023,7 +19910,7 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C258">
         <v>2030</v>
@@ -19064,7 +19951,7 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C259">
         <v>2035</v>
@@ -19105,7 +19992,7 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C260">
         <v>2040</v>
@@ -19146,7 +20033,7 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C261">
         <v>2045</v>
@@ -19187,7 +20074,7 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C262">
         <v>2050</v>
@@ -19228,7 +20115,7 @@
         <v>2</v>
       </c>
       <c r="B263" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C263">
         <v>2020</v>
@@ -19269,7 +20156,7 @@
         <v>2</v>
       </c>
       <c r="B264" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C264">
         <v>2025</v>
@@ -19310,7 +20197,7 @@
         <v>2</v>
       </c>
       <c r="B265" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C265">
         <v>2030</v>
@@ -19351,7 +20238,7 @@
         <v>2</v>
       </c>
       <c r="B266" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C266">
         <v>2035</v>
@@ -19392,7 +20279,7 @@
         <v>2</v>
       </c>
       <c r="B267" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C267">
         <v>2040</v>
@@ -19433,7 +20320,7 @@
         <v>2</v>
       </c>
       <c r="B268" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C268">
         <v>2045</v>
@@ -19474,7 +20361,7 @@
         <v>2</v>
       </c>
       <c r="B269" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C269">
         <v>2050</v>
@@ -19515,7 +20402,7 @@
         <v>5</v>
       </c>
       <c r="B270" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C270">
         <v>2020</v>
@@ -19556,7 +20443,7 @@
         <v>5</v>
       </c>
       <c r="B271" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C271">
         <v>2025</v>
@@ -19597,7 +20484,7 @@
         <v>5</v>
       </c>
       <c r="B272" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C272">
         <v>2030</v>
@@ -19638,7 +20525,7 @@
         <v>5</v>
       </c>
       <c r="B273" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C273">
         <v>2035</v>
@@ -19679,7 +20566,7 @@
         <v>5</v>
       </c>
       <c r="B274" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C274">
         <v>2040</v>
@@ -19720,7 +20607,7 @@
         <v>5</v>
       </c>
       <c r="B275" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C275">
         <v>2045</v>
@@ -19761,7 +20648,7 @@
         <v>5</v>
       </c>
       <c r="B276" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C276">
         <v>2050</v>
@@ -19802,7 +20689,7 @@
         <v>7</v>
       </c>
       <c r="B277" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C277">
         <v>2020</v>
@@ -19843,7 +20730,7 @@
         <v>7</v>
       </c>
       <c r="B278" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C278">
         <v>2025</v>
@@ -19884,7 +20771,7 @@
         <v>7</v>
       </c>
       <c r="B279" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C279">
         <v>2030</v>
@@ -19925,7 +20812,7 @@
         <v>7</v>
       </c>
       <c r="B280" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C280">
         <v>2035</v>
@@ -19966,7 +20853,7 @@
         <v>7</v>
       </c>
       <c r="B281" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C281">
         <v>2040</v>
@@ -20007,7 +20894,7 @@
         <v>7</v>
       </c>
       <c r="B282" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C282">
         <v>2045</v>
@@ -20048,7 +20935,7 @@
         <v>7</v>
       </c>
       <c r="B283" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C283">
         <v>2050</v>
@@ -20089,7 +20976,7 @@
         <v>9</v>
       </c>
       <c r="B284" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C284">
         <v>2020</v>
@@ -20130,7 +21017,7 @@
         <v>9</v>
       </c>
       <c r="B285" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C285">
         <v>2025</v>
@@ -20171,7 +21058,7 @@
         <v>9</v>
       </c>
       <c r="B286" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C286">
         <v>2030</v>
@@ -20212,7 +21099,7 @@
         <v>9</v>
       </c>
       <c r="B287" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C287">
         <v>2035</v>
@@ -20253,7 +21140,7 @@
         <v>9</v>
       </c>
       <c r="B288" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C288">
         <v>2040</v>
@@ -20294,7 +21181,7 @@
         <v>9</v>
       </c>
       <c r="B289" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C289">
         <v>2045</v>
@@ -20335,7 +21222,7 @@
         <v>9</v>
       </c>
       <c r="B290" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C290">
         <v>2050</v>
@@ -20376,7 +21263,7 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C291">
         <v>2020</v>
@@ -20417,7 +21304,7 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C292">
         <v>2025</v>
@@ -20458,7 +21345,7 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C293">
         <v>2030</v>
@@ -20499,7 +21386,7 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C294">
         <v>2035</v>
@@ -20540,7 +21427,7 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C295">
         <v>2040</v>
@@ -20581,7 +21468,7 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C296">
         <v>2045</v>
@@ -20622,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C297">
         <v>2050</v>
@@ -20663,7 +21550,7 @@
         <v>2</v>
       </c>
       <c r="B298" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C298">
         <v>2020</v>
@@ -20704,7 +21591,7 @@
         <v>2</v>
       </c>
       <c r="B299" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C299">
         <v>2025</v>
@@ -20745,7 +21632,7 @@
         <v>2</v>
       </c>
       <c r="B300" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C300">
         <v>2030</v>
@@ -20786,7 +21673,7 @@
         <v>2</v>
       </c>
       <c r="B301" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C301">
         <v>2035</v>
@@ -20827,7 +21714,7 @@
         <v>2</v>
       </c>
       <c r="B302" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C302">
         <v>2040</v>
@@ -20868,7 +21755,7 @@
         <v>2</v>
       </c>
       <c r="B303" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C303">
         <v>2045</v>
@@ -20909,7 +21796,7 @@
         <v>2</v>
       </c>
       <c r="B304" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C304">
         <v>2050</v>
@@ -20950,7 +21837,7 @@
         <v>5</v>
       </c>
       <c r="B305" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C305">
         <v>2020</v>
@@ -20991,7 +21878,7 @@
         <v>5</v>
       </c>
       <c r="B306" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C306">
         <v>2025</v>
@@ -21032,7 +21919,7 @@
         <v>5</v>
       </c>
       <c r="B307" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C307">
         <v>2030</v>
@@ -21073,7 +21960,7 @@
         <v>5</v>
       </c>
       <c r="B308" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C308">
         <v>2035</v>
@@ -21114,7 +22001,7 @@
         <v>5</v>
       </c>
       <c r="B309" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C309">
         <v>2040</v>
@@ -21155,7 +22042,7 @@
         <v>5</v>
       </c>
       <c r="B310" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C310">
         <v>2045</v>
@@ -21196,7 +22083,7 @@
         <v>5</v>
       </c>
       <c r="B311" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C311">
         <v>2050</v>
@@ -21237,7 +22124,7 @@
         <v>7</v>
       </c>
       <c r="B312" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C312">
         <v>2020</v>
@@ -21278,7 +22165,7 @@
         <v>7</v>
       </c>
       <c r="B313" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C313">
         <v>2025</v>
@@ -21319,7 +22206,7 @@
         <v>7</v>
       </c>
       <c r="B314" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C314">
         <v>2030</v>
@@ -21360,7 +22247,7 @@
         <v>7</v>
       </c>
       <c r="B315" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C315">
         <v>2035</v>
@@ -21401,7 +22288,7 @@
         <v>7</v>
       </c>
       <c r="B316" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C316">
         <v>2040</v>
@@ -21442,7 +22329,7 @@
         <v>7</v>
       </c>
       <c r="B317" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C317">
         <v>2045</v>
@@ -21483,7 +22370,7 @@
         <v>7</v>
       </c>
       <c r="B318" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C318">
         <v>2050</v>
@@ -21524,7 +22411,7 @@
         <v>9</v>
       </c>
       <c r="B319" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C319">
         <v>2020</v>
@@ -21565,7 +22452,7 @@
         <v>9</v>
       </c>
       <c r="B320" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C320">
         <v>2025</v>
@@ -21606,7 +22493,7 @@
         <v>9</v>
       </c>
       <c r="B321" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C321">
         <v>2030</v>
@@ -21647,7 +22534,7 @@
         <v>9</v>
       </c>
       <c r="B322" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C322">
         <v>2035</v>
@@ -21688,7 +22575,7 @@
         <v>9</v>
       </c>
       <c r="B323" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C323">
         <v>2040</v>
@@ -21729,7 +22616,7 @@
         <v>9</v>
       </c>
       <c r="B324" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C324">
         <v>2045</v>
@@ -21770,7 +22657,7 @@
         <v>9</v>
       </c>
       <c r="B325" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C325">
         <v>2050</v>
@@ -21811,7 +22698,7 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C326">
         <v>2020</v>
@@ -21852,7 +22739,7 @@
         <v>0</v>
       </c>
       <c r="B327" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C327">
         <v>2025</v>
@@ -21893,7 +22780,7 @@
         <v>0</v>
       </c>
       <c r="B328" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C328">
         <v>2030</v>
@@ -21934,7 +22821,7 @@
         <v>0</v>
       </c>
       <c r="B329" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C329">
         <v>2035</v>
@@ -21975,7 +22862,7 @@
         <v>0</v>
       </c>
       <c r="B330" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C330">
         <v>2040</v>
@@ -22016,7 +22903,7 @@
         <v>0</v>
       </c>
       <c r="B331" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C331">
         <v>2045</v>
@@ -22057,7 +22944,7 @@
         <v>0</v>
       </c>
       <c r="B332" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C332">
         <v>2050</v>
@@ -22098,7 +22985,7 @@
         <v>2</v>
       </c>
       <c r="B333" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C333">
         <v>2020</v>
@@ -22139,7 +23026,7 @@
         <v>2</v>
       </c>
       <c r="B334" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C334">
         <v>2025</v>
@@ -22180,7 +23067,7 @@
         <v>2</v>
       </c>
       <c r="B335" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C335">
         <v>2030</v>
@@ -22221,7 +23108,7 @@
         <v>2</v>
       </c>
       <c r="B336" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C336">
         <v>2035</v>
@@ -22262,7 +23149,7 @@
         <v>2</v>
       </c>
       <c r="B337" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C337">
         <v>2040</v>
@@ -22303,7 +23190,7 @@
         <v>2</v>
       </c>
       <c r="B338" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C338">
         <v>2045</v>
@@ -22344,7 +23231,7 @@
         <v>2</v>
       </c>
       <c r="B339" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C339">
         <v>2050</v>
@@ -22385,7 +23272,7 @@
         <v>5</v>
       </c>
       <c r="B340" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C340">
         <v>2020</v>
@@ -22426,7 +23313,7 @@
         <v>5</v>
       </c>
       <c r="B341" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C341">
         <v>2025</v>
@@ -22467,7 +23354,7 @@
         <v>5</v>
       </c>
       <c r="B342" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C342">
         <v>2030</v>
@@ -22508,7 +23395,7 @@
         <v>5</v>
       </c>
       <c r="B343" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C343">
         <v>2035</v>
@@ -22549,7 +23436,7 @@
         <v>5</v>
       </c>
       <c r="B344" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C344">
         <v>2040</v>
@@ -22590,7 +23477,7 @@
         <v>5</v>
       </c>
       <c r="B345" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C345">
         <v>2045</v>
@@ -22631,7 +23518,7 @@
         <v>5</v>
       </c>
       <c r="B346" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C346">
         <v>2050</v>
@@ -22672,7 +23559,7 @@
         <v>7</v>
       </c>
       <c r="B347" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C347">
         <v>2020</v>
@@ -22713,7 +23600,7 @@
         <v>7</v>
       </c>
       <c r="B348" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C348">
         <v>2025</v>
@@ -22754,7 +23641,7 @@
         <v>7</v>
       </c>
       <c r="B349" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C349">
         <v>2030</v>
@@ -22795,7 +23682,7 @@
         <v>7</v>
       </c>
       <c r="B350" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C350">
         <v>2035</v>
@@ -22836,7 +23723,7 @@
         <v>7</v>
       </c>
       <c r="B351" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C351">
         <v>2040</v>
@@ -22877,7 +23764,7 @@
         <v>7</v>
       </c>
       <c r="B352" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C352">
         <v>2045</v>
@@ -22918,7 +23805,7 @@
         <v>7</v>
       </c>
       <c r="B353" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C353">
         <v>2050</v>
@@ -22959,7 +23846,7 @@
         <v>9</v>
       </c>
       <c r="B354" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C354">
         <v>2020</v>
@@ -23000,7 +23887,7 @@
         <v>9</v>
       </c>
       <c r="B355" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C355">
         <v>2025</v>
@@ -23041,7 +23928,7 @@
         <v>9</v>
       </c>
       <c r="B356" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C356">
         <v>2030</v>
@@ -23082,7 +23969,7 @@
         <v>9</v>
       </c>
       <c r="B357" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C357">
         <v>2035</v>
@@ -23123,7 +24010,7 @@
         <v>9</v>
       </c>
       <c r="B358" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C358">
         <v>2040</v>
@@ -23164,7 +24051,7 @@
         <v>9</v>
       </c>
       <c r="B359" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C359">
         <v>2045</v>
@@ -23205,7 +24092,7 @@
         <v>9</v>
       </c>
       <c r="B360" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C360">
         <v>2050</v>
@@ -23246,7 +24133,7 @@
         <v>0</v>
       </c>
       <c r="B361" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C361">
         <v>2020</v>
@@ -23287,7 +24174,7 @@
         <v>0</v>
       </c>
       <c r="B362" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C362">
         <v>2025</v>
@@ -23328,7 +24215,7 @@
         <v>0</v>
       </c>
       <c r="B363" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C363">
         <v>2030</v>
@@ -23369,7 +24256,7 @@
         <v>0</v>
       </c>
       <c r="B364" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C364">
         <v>2035</v>
@@ -23410,7 +24297,7 @@
         <v>0</v>
       </c>
       <c r="B365" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C365">
         <v>2040</v>
@@ -23451,7 +24338,7 @@
         <v>0</v>
       </c>
       <c r="B366" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C366">
         <v>2045</v>
@@ -23492,7 +24379,7 @@
         <v>0</v>
       </c>
       <c r="B367" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C367">
         <v>2050</v>
@@ -23533,7 +24420,7 @@
         <v>2</v>
       </c>
       <c r="B368" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C368">
         <v>2020</v>
@@ -23574,7 +24461,7 @@
         <v>2</v>
       </c>
       <c r="B369" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C369">
         <v>2025</v>
@@ -23615,7 +24502,7 @@
         <v>2</v>
       </c>
       <c r="B370" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C370">
         <v>2030</v>
@@ -23656,7 +24543,7 @@
         <v>2</v>
       </c>
       <c r="B371" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C371">
         <v>2035</v>
@@ -23697,7 +24584,7 @@
         <v>2</v>
       </c>
       <c r="B372" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C372">
         <v>2040</v>
@@ -23738,7 +24625,7 @@
         <v>2</v>
       </c>
       <c r="B373" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C373">
         <v>2045</v>
@@ -23779,7 +24666,7 @@
         <v>2</v>
       </c>
       <c r="B374" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C374">
         <v>2050</v>
@@ -23820,7 +24707,7 @@
         <v>5</v>
       </c>
       <c r="B375" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C375">
         <v>2020</v>
@@ -23861,7 +24748,7 @@
         <v>5</v>
       </c>
       <c r="B376" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C376">
         <v>2025</v>
@@ -23902,7 +24789,7 @@
         <v>5</v>
       </c>
       <c r="B377" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C377">
         <v>2030</v>
@@ -23943,7 +24830,7 @@
         <v>5</v>
       </c>
       <c r="B378" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C378">
         <v>2035</v>
@@ -23984,7 +24871,7 @@
         <v>5</v>
       </c>
       <c r="B379" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C379">
         <v>2040</v>
@@ -24025,7 +24912,7 @@
         <v>5</v>
       </c>
       <c r="B380" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C380">
         <v>2045</v>
@@ -24066,7 +24953,7 @@
         <v>5</v>
       </c>
       <c r="B381" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C381">
         <v>2050</v>
@@ -24107,7 +24994,7 @@
         <v>7</v>
       </c>
       <c r="B382" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C382">
         <v>2020</v>
@@ -24148,7 +25035,7 @@
         <v>7</v>
       </c>
       <c r="B383" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C383">
         <v>2025</v>
@@ -24189,7 +25076,7 @@
         <v>7</v>
       </c>
       <c r="B384" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C384">
         <v>2030</v>
@@ -24230,7 +25117,7 @@
         <v>7</v>
       </c>
       <c r="B385" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C385">
         <v>2035</v>
@@ -24271,7 +25158,7 @@
         <v>7</v>
       </c>
       <c r="B386" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C386">
         <v>2040</v>
@@ -24312,7 +25199,7 @@
         <v>7</v>
       </c>
       <c r="B387" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C387">
         <v>2045</v>
@@ -24353,7 +25240,7 @@
         <v>7</v>
       </c>
       <c r="B388" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C388">
         <v>2050</v>
@@ -24394,7 +25281,7 @@
         <v>9</v>
       </c>
       <c r="B389" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C389">
         <v>2020</v>
@@ -24435,7 +25322,7 @@
         <v>9</v>
       </c>
       <c r="B390" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C390">
         <v>2025</v>
@@ -24476,7 +25363,7 @@
         <v>9</v>
       </c>
       <c r="B391" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C391">
         <v>2030</v>
@@ -24517,7 +25404,7 @@
         <v>9</v>
       </c>
       <c r="B392" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C392">
         <v>2035</v>
@@ -24558,7 +25445,7 @@
         <v>9</v>
       </c>
       <c r="B393" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C393">
         <v>2040</v>
@@ -24599,7 +25486,7 @@
         <v>9</v>
       </c>
       <c r="B394" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C394">
         <v>2045</v>
@@ -24640,7 +25527,7 @@
         <v>9</v>
       </c>
       <c r="B395" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C395">
         <v>2050</v>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C9B7A2-C1F2-4C28-A7B5-AECC7458E636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57204256-70CD-4BA6-8E96-29A1329AD2C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -517,7 +517,7 @@
     <t>aggregators,grid</t>
   </si>
   <si>
-    <t>9-32</t>
+    <t>1-32</t>
   </si>
 </sst>
 </file>
@@ -6109,7 +6109,7 @@
     <row r="2" spans="1:41" x14ac:dyDescent="0.45">
       <c r="D2" s="1" t="str">
         <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,I1:EG1)</f>
-        <v>~Inputcell: 9-32</v>
+        <v>~Inputcell: 1-32</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>26</v>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57204256-70CD-4BA6-8E96-29A1329AD2C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CBD00F-FFC0-4773-A042-02B9548F355E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ar6_r10!$A$10:$M$395</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Veda!$B$8:$E$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Veda!$C$8:$G$40</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="146">
   <si>
     <t>C1</t>
   </si>
@@ -515,9 +515,6 @@
   </si>
   <si>
     <t>aggregators,grid</t>
-  </si>
-  <si>
-    <t>1-32</t>
   </si>
 </sst>
 </file>
@@ -1034,22 +1031,22 @@
                   <c:v>1811.6499999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2355.145</c:v>
+                  <c:v>2445.7275</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2934.873</c:v>
+                  <c:v>3097.9214999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3840.6979999999999</c:v>
+                  <c:v>4021.8629999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4782.7560000000003</c:v>
+                  <c:v>4728.4064999999991</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6213.9594999999999</c:v>
+                  <c:v>5905.9789999999994</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7445.8815000000004</c:v>
+                  <c:v>6449.4739999999993</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1472,15 +1469,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>454817</xdr:colOff>
+      <xdr:colOff>283367</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>309562</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>95248</xdr:rowOff>
+      <xdr:colOff>138112</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>176211</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6102,14 +6099,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.45">
-      <c r="I1" s="21" t="s">
-        <v>146</v>
+      <c r="I1" s="21"/>
+      <c r="J1">
+        <v>1</v>
+      </c>
+      <c r="K1">
+        <v>4</v>
+      </c>
+      <c r="L1">
+        <v>5</v>
+      </c>
+      <c r="M1">
+        <v>8</v>
+      </c>
+      <c r="N1">
+        <v>9</v>
+      </c>
+      <c r="O1">
+        <v>12</v>
+      </c>
+      <c r="P1">
+        <v>13</v>
+      </c>
+      <c r="Q1">
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.45">
       <c r="D2" s="1" t="str">
         <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,I1:EG1)</f>
-        <v>~Inputcell: 1-32</v>
+        <v>~Inputcell: 1,4,5,8,9,12,13,16</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>26</v>
@@ -6134,7 +6153,7 @@
         <v>114</v>
       </c>
       <c r="Q3" s="10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.45">
@@ -6148,7 +6167,7 @@
         <v>82</v>
       </c>
       <c r="Q4" s="10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.45">
@@ -6498,35 +6517,35 @@
       </c>
       <c r="J14" s="3" t="str">
         <f>VLOOKUP($D$5,$P$3:$Q$5,2,FALSE)</f>
-        <v>C3</v>
+        <v>C7</v>
       </c>
       <c r="K14" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$E$5,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
         <v>0</v>
       </c>
       <c r="L14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
-        <v>1.3</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
+        <v>1.35</v>
       </c>
       <c r="M14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
-        <v>1.62</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
+        <v>1.71</v>
       </c>
       <c r="N14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
-        <v>2.12</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
+        <v>2.2200000000000002</v>
       </c>
       <c r="O14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
-        <v>2.64</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
+        <v>2.61</v>
       </c>
       <c r="P14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
-        <v>3.43</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
+        <v>3.26</v>
       </c>
       <c r="Q14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
-        <v>4.1100000000000003</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
+        <v>3.56</v>
       </c>
       <c r="V14" s="8">
         <f>U11</f>
@@ -6534,27 +6553,27 @@
       </c>
       <c r="W14" s="8">
         <f t="shared" ref="W14:AB14" si="4">$U$11*L14</f>
-        <v>2355.145</v>
+        <v>2445.7275</v>
       </c>
       <c r="X14" s="8">
         <f t="shared" si="4"/>
-        <v>2934.873</v>
+        <v>3097.9214999999999</v>
       </c>
       <c r="Y14" s="8">
         <f t="shared" si="4"/>
-        <v>3840.6979999999999</v>
+        <v>4021.8629999999998</v>
       </c>
       <c r="Z14" s="8">
         <f t="shared" si="4"/>
-        <v>4782.7560000000003</v>
+        <v>4728.4064999999991</v>
       </c>
       <c r="AA14" s="8">
         <f t="shared" si="4"/>
-        <v>6213.9594999999999</v>
+        <v>5905.9789999999994</v>
       </c>
       <c r="AB14" s="8">
         <f t="shared" si="4"/>
-        <v>7445.8815000000004</v>
+        <v>6449.4739999999993</v>
       </c>
       <c r="AI14">
         <v>6</v>
@@ -6604,28 +6623,28 @@
         <v>0</v>
       </c>
       <c r="L15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
-        <v>2.33</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
+        <v>1.23</v>
       </c>
       <c r="M15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
-        <v>4.4000000000000004</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
+        <v>1.3</v>
       </c>
       <c r="N15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
-        <v>7.61</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
+        <v>2.71</v>
       </c>
       <c r="O15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
-        <v>11.44</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
+        <v>2.94</v>
       </c>
       <c r="P15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
-        <v>19.03</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
+        <v>5.92</v>
       </c>
       <c r="Q15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
-        <v>25.28</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
+        <v>5.41</v>
       </c>
       <c r="AI15">
         <v>7</v>
@@ -6806,7 +6825,7 @@
       </c>
       <c r="K18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I18)</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I18)</f>
@@ -6814,7 +6833,7 @@
       </c>
       <c r="M18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I18)</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="N18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I18)</f>
@@ -6837,7 +6856,7 @@
       </c>
       <c r="V18" s="6">
         <f t="shared" ref="V18:AB20" si="7">K18*V$14</f>
-        <v>0</v>
+        <v>18.116499999999998</v>
       </c>
       <c r="W18" s="6">
         <f t="shared" si="7"/>
@@ -6845,23 +6864,23 @@
       </c>
       <c r="X18" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>30.979215</v>
       </c>
       <c r="Y18" s="6">
         <f t="shared" si="7"/>
-        <v>38.406979999999997</v>
+        <v>40.218629999999997</v>
       </c>
       <c r="Z18" s="6">
         <f t="shared" si="7"/>
-        <v>95.655120000000011</v>
+        <v>94.568129999999982</v>
       </c>
       <c r="AA18" s="6">
         <f t="shared" si="7"/>
-        <v>124.27919</v>
+        <v>118.11957999999998</v>
       </c>
       <c r="AB18" s="6">
         <f t="shared" si="7"/>
-        <v>223.37644500000002</v>
+        <v>193.48421999999997</v>
       </c>
       <c r="AC18" t="s">
         <v>17</v>
@@ -6910,62 +6929,62 @@
       </c>
       <c r="K19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
       <c r="L19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="M19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="N19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="O19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="P19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="Q19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="U19" s="10" t="s">
         <v>19</v>
       </c>
       <c r="V19" s="6">
         <f t="shared" si="7"/>
-        <v>887.70849999999996</v>
+        <v>960.17449999999997</v>
       </c>
       <c r="W19" s="6">
         <f t="shared" si="7"/>
-        <v>1154.0210500000001</v>
+        <v>1222.86375</v>
       </c>
       <c r="X19" s="6">
         <f t="shared" si="7"/>
-        <v>1350.0415800000001</v>
+        <v>1610.9191800000001</v>
       </c>
       <c r="Y19" s="6">
         <f t="shared" si="7"/>
-        <v>1843.5350399999998</v>
+        <v>2010.9314999999999</v>
       </c>
       <c r="Z19" s="6">
         <f t="shared" si="7"/>
-        <v>2200.0677600000004</v>
+        <v>2222.3510549999996</v>
       </c>
       <c r="AA19" s="6">
         <f t="shared" si="7"/>
-        <v>2982.7005599999998</v>
+        <v>2775.8101299999994</v>
       </c>
       <c r="AB19" s="6">
         <f t="shared" si="7"/>
-        <v>3499.5643049999999</v>
+        <v>2902.2632999999996</v>
       </c>
       <c r="AC19" t="s">
         <v>17</v>
@@ -7013,62 +7032,62 @@
       </c>
       <c r="K20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="L20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="M20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="N20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="O20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="P20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="Q20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="U20" s="10" t="s">
         <v>22</v>
       </c>
       <c r="V20" s="6">
         <f t="shared" si="7"/>
-        <v>833.35899999999992</v>
+        <v>815.24249999999995</v>
       </c>
       <c r="W20" s="6">
         <f t="shared" si="7"/>
-        <v>1106.91815</v>
+        <v>1100.5773750000001</v>
       </c>
       <c r="X20" s="6">
         <f t="shared" si="7"/>
-        <v>1320.6928500000001</v>
+        <v>1363.08546</v>
       </c>
       <c r="Y20" s="6">
         <f t="shared" si="7"/>
-        <v>1728.3141000000001</v>
+        <v>1769.6197199999999</v>
       </c>
       <c r="Z20" s="6">
         <f t="shared" si="7"/>
-        <v>2247.8953200000001</v>
+        <v>2127.7829249999995</v>
       </c>
       <c r="AA20" s="6">
         <f t="shared" si="7"/>
-        <v>2734.1421799999998</v>
+        <v>2716.7503399999996</v>
       </c>
       <c r="AB20" s="6">
         <f t="shared" si="7"/>
-        <v>3276.18786</v>
+        <v>3031.2527799999993</v>
       </c>
       <c r="AC20" t="s">
         <v>17</v>
@@ -7121,7 +7140,7 @@
       </c>
       <c r="L21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I21)</f>
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="M21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I21)</f>
@@ -7133,15 +7152,15 @@
       </c>
       <c r="O21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I21)</f>
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="P21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I21)</f>
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="Q21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I21)</f>
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="U21" s="10" t="s">
         <v>24</v>
@@ -7215,31 +7234,31 @@
       </c>
       <c r="V22" s="6">
         <f t="shared" ref="V22:AB22" si="10">V14-SUM(V19:V21)</f>
-        <v>54.349500000000035</v>
+        <v>0</v>
       </c>
       <c r="W22" s="6">
         <f t="shared" si="10"/>
-        <v>57.972800000000007</v>
+        <v>86.053374999999505</v>
       </c>
       <c r="X22" s="6">
         <f t="shared" si="10"/>
-        <v>227.90556999999944</v>
+        <v>87.68385999999964</v>
       </c>
       <c r="Y22" s="6">
         <f t="shared" si="10"/>
-        <v>232.61585999999988</v>
+        <v>205.07877999999982</v>
       </c>
       <c r="Z22" s="6">
         <f t="shared" si="10"/>
-        <v>298.55991999999969</v>
+        <v>342.03952000000027</v>
       </c>
       <c r="AA22" s="6">
         <f t="shared" si="10"/>
-        <v>460.88375999999971</v>
+        <v>377.18553000000065</v>
       </c>
       <c r="AB22" s="6">
         <f t="shared" si="10"/>
-        <v>633.89633500000036</v>
+        <v>479.72491999999966</v>
       </c>
       <c r="AC22" t="s">
         <v>17</v>
@@ -8316,7 +8335,7 @@
       </c>
       <c r="Q48">
         <f>VLOOKUP($J$14,$AM$9:$AO$15,3,FALSE)*K48</f>
-        <v>55.5</v>
+        <v>27.75</v>
       </c>
       <c r="T48">
         <f>HLOOKUP($I48&amp;"_"&amp;T$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CBD00F-FFC0-4773-A042-02B9548F355E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D71D69-04EF-4761-9DE1-85F99E83C73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8334,8 +8334,8 @@
         <v>18.5</v>
       </c>
       <c r="Q48">
-        <f>VLOOKUP($J$14,$AM$9:$AO$15,3,FALSE)*K48</f>
-        <v>27.75</v>
+        <f>K48*2.5</f>
+        <v>46.25</v>
       </c>
       <c r="T48">
         <f>HLOOKUP($I48&amp;"_"&amp;T$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D71D69-04EF-4761-9DE1-85F99E83C73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7CBD59-50BA-41DA-A6B0-D4DC1B1B1619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7893,32 +7893,32 @@
         <v>73</v>
       </c>
       <c r="K37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
         <v>1</v>
       </c>
       <c r="L37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
-        <v>1.1100000000000001</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
+        <v>1.04</v>
       </c>
       <c r="M37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
-        <v>1.21</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
+        <v>1.1000000000000001</v>
       </c>
       <c r="N37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
-        <v>1.1599999999999999</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
+        <v>1.08</v>
       </c>
       <c r="O37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
-        <v>1.36</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
+        <v>1.24</v>
       </c>
       <c r="P37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
-        <v>1.4</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
+        <v>1.3</v>
       </c>
       <c r="Q37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
-        <v>1.44</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I37)</f>
+        <v>1.33</v>
       </c>
       <c r="AL37" s="10">
         <f t="shared" si="5"/>
@@ -7954,32 +7954,32 @@
         <v>74</v>
       </c>
       <c r="K38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
         <v>1</v>
       </c>
       <c r="L38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
-        <v>1.07</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
+        <v>1.06</v>
       </c>
       <c r="M38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="N38" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
         <v>1.17</v>
       </c>
-      <c r="N38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
-        <v>1.21</v>
-      </c>
       <c r="O38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
-        <v>1.37</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
+        <v>1.22</v>
       </c>
       <c r="P38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
-        <v>1.33</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
+        <v>1.26</v>
       </c>
       <c r="Q38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
-        <v>1.52</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I38)</f>
+        <v>1.3</v>
       </c>
       <c r="AL38" s="10">
         <f t="shared" si="5"/>
@@ -8015,32 +8015,32 @@
         <v>75</v>
       </c>
       <c r="K39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
         <v>1</v>
       </c>
       <c r="L39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
-        <v>1.43</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
+        <v>1.08</v>
       </c>
       <c r="M39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
-        <v>1.58</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
+        <v>1.1399999999999999</v>
       </c>
       <c r="N39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
-        <v>1.53</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
+        <v>1.2</v>
       </c>
       <c r="O39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
-        <v>1.74</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
+        <v>1.27</v>
       </c>
       <c r="P39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
-        <v>1.94</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
+        <v>1.3</v>
       </c>
       <c r="Q39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
-        <v>2.2000000000000002</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I39)</f>
+        <v>1.32</v>
       </c>
       <c r="AL39" s="10">
         <f t="shared" si="5"/>
@@ -8076,32 +8076,32 @@
         <v>76</v>
       </c>
       <c r="K40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
         <v>1</v>
       </c>
       <c r="L40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
         <v>1.05</v>
       </c>
       <c r="M40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
-        <v>1.06</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
+        <v>1.03</v>
       </c>
       <c r="N40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
-        <v>1.04</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
+        <v>0.98</v>
       </c>
       <c r="O40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
-        <v>1</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
+        <v>0.99</v>
       </c>
       <c r="P40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
-        <v>0.95</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
+        <v>0.93</v>
       </c>
       <c r="Q40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
-        <v>0.93</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$I$36,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I40)</f>
+        <v>0.91</v>
       </c>
       <c r="AL40" s="10">
         <f t="shared" si="5"/>
@@ -8183,32 +8183,32 @@
         <v>Gas</v>
       </c>
       <c r="K45">
-        <f t="shared" ref="K45:Q48" si="16">AVERAGE($T45:$U45)*K37</f>
-        <v>36</v>
+        <f>AVERAGE($T45)*K37</f>
+        <v>30.9</v>
       </c>
       <c r="L45">
-        <f t="shared" si="16"/>
-        <v>39.96</v>
+        <f t="shared" ref="L45:Q45" si="16">AVERAGE($T45)*L37</f>
+        <v>32.136000000000003</v>
       </c>
       <c r="M45">
         <f t="shared" si="16"/>
-        <v>43.56</v>
+        <v>33.99</v>
       </c>
       <c r="N45">
         <f t="shared" si="16"/>
-        <v>41.76</v>
+        <v>33.372</v>
       </c>
       <c r="O45">
         <f t="shared" si="16"/>
-        <v>48.96</v>
+        <v>38.315999999999995</v>
       </c>
       <c r="P45">
         <f t="shared" si="16"/>
-        <v>50.4</v>
+        <v>40.17</v>
       </c>
       <c r="Q45">
         <f t="shared" si="16"/>
-        <v>51.839999999999996</v>
+        <v>41.097000000000001</v>
       </c>
       <c r="T45">
         <f>HLOOKUP($I45&amp;"_"&amp;T$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
@@ -8232,32 +8232,32 @@
         <v>Coal</v>
       </c>
       <c r="K46">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="K45:Q48" si="18">AVERAGE($T46:$U46)*K38</f>
         <v>9.8000000000000007</v>
       </c>
       <c r="L46">
-        <f t="shared" si="16"/>
-        <v>10.486000000000001</v>
+        <f t="shared" si="18"/>
+        <v>10.388000000000002</v>
       </c>
       <c r="M46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
+        <v>11.074</v>
+      </c>
+      <c r="N46">
+        <f t="shared" si="18"/>
         <v>11.465999999999999</v>
       </c>
-      <c r="N46">
-        <f t="shared" si="16"/>
-        <v>11.858000000000001</v>
-      </c>
       <c r="O46">
-        <f t="shared" si="16"/>
-        <v>13.426000000000002</v>
+        <f t="shared" si="18"/>
+        <v>11.956000000000001</v>
       </c>
       <c r="P46">
-        <f t="shared" si="16"/>
-        <v>13.034000000000002</v>
+        <f t="shared" si="18"/>
+        <v>12.348000000000001</v>
       </c>
       <c r="Q46">
-        <f t="shared" si="16"/>
-        <v>14.896000000000001</v>
+        <f t="shared" si="18"/>
+        <v>12.740000000000002</v>
       </c>
       <c r="T46">
         <f>HLOOKUP($I46&amp;"_"&amp;T$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
@@ -8281,32 +8281,32 @@
         <v>Oil</v>
       </c>
       <c r="K47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>50</v>
       </c>
       <c r="L47">
-        <f t="shared" si="16"/>
-        <v>71.5</v>
+        <f t="shared" si="18"/>
+        <v>54</v>
       </c>
       <c r="M47">
-        <f t="shared" si="16"/>
-        <v>79</v>
+        <f t="shared" si="18"/>
+        <v>56.999999999999993</v>
       </c>
       <c r="N47">
-        <f t="shared" si="16"/>
-        <v>76.5</v>
+        <f t="shared" si="18"/>
+        <v>60</v>
       </c>
       <c r="O47">
-        <f t="shared" si="16"/>
-        <v>87</v>
+        <f t="shared" si="18"/>
+        <v>63.5</v>
       </c>
       <c r="P47">
-        <f t="shared" si="16"/>
-        <v>97</v>
+        <f t="shared" si="18"/>
+        <v>65</v>
       </c>
       <c r="Q47">
-        <f t="shared" si="16"/>
-        <v>110.00000000000001</v>
+        <f t="shared" si="18"/>
+        <v>66</v>
       </c>
       <c r="T47">
         <f>HLOOKUP($I47&amp;"_"&amp;T$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
@@ -8330,7 +8330,7 @@
         <v>Bioenergy</v>
       </c>
       <c r="K48">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>18.5</v>
       </c>
       <c r="Q48">

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7CBD59-50BA-41DA-A6B0-D4DC1B1B1619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9459AA5F-0716-4D6F-84B2-E17D7B1E83E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="147">
   <si>
     <t>C1</t>
   </si>
@@ -515,6 +515,9 @@
   </si>
   <si>
     <t>aggregators,grid</t>
+  </si>
+  <si>
+    <t>1-32</t>
   </si>
 </sst>
 </file>
@@ -6099,36 +6102,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.45">
-      <c r="I1" s="21"/>
-      <c r="J1">
-        <v>1</v>
-      </c>
-      <c r="K1">
-        <v>4</v>
-      </c>
-      <c r="L1">
-        <v>5</v>
-      </c>
-      <c r="M1">
-        <v>8</v>
-      </c>
-      <c r="N1">
-        <v>9</v>
-      </c>
-      <c r="O1">
-        <v>12</v>
-      </c>
-      <c r="P1">
-        <v>13</v>
-      </c>
-      <c r="Q1">
-        <v>16</v>
+      <c r="I1" s="21" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.45">
       <c r="D2" s="1" t="str">
         <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,I1:EG1)</f>
-        <v>~Inputcell: 1,4,5,8,9,12,13,16</v>
+        <v>~Inputcell: 1-32</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>26</v>
@@ -8232,7 +8213,7 @@
         <v>Coal</v>
       </c>
       <c r="K46">
-        <f t="shared" ref="K45:Q48" si="18">AVERAGE($T46:$U46)*K38</f>
+        <f t="shared" ref="K46:Q48" si="18">AVERAGE($T46:$U46)*K38</f>
         <v>9.8000000000000007</v>
       </c>
       <c r="L46">

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9459AA5F-0716-4D6F-84B2-E17D7B1E83E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFDA3B42-376B-4FE8-9FC8-16D7A15856B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1816" uniqueCount="147">
   <si>
     <t>C1</t>
   </si>
@@ -517,7 +517,7 @@
     <t>aggregators,grid</t>
   </si>
   <si>
-    <t>1-32</t>
+    <t>33-40</t>
   </si>
 </sst>
 </file>
@@ -1034,22 +1034,22 @@
                   <c:v>1811.6499999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2445.7275</c:v>
+                  <c:v>2228.3294999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3097.9214999999999</c:v>
+                  <c:v>2789.9409999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4021.8629999999998</c:v>
+                  <c:v>3279.0864999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4728.4064999999991</c:v>
+                  <c:v>3840.6979999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5905.9789999999994</c:v>
+                  <c:v>4655.9404999999997</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6449.4739999999993</c:v>
+                  <c:v>5163.2024999999994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1325,19 +1325,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>176.95</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>242.69</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>325.37</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>430.26</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>592.32000000000005</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6109,7 +6109,7 @@
     <row r="2" spans="1:41" x14ac:dyDescent="0.45">
       <c r="D2" s="1" t="str">
         <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,I1:EG1)</f>
-        <v>~Inputcell: 1-32</v>
+        <v>~Inputcell: 33-40</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>26</v>
@@ -6122,13 +6122,13 @@
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.45">
       <c r="D3" s="9">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="M3" s="10">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="P3" s="10" t="s">
         <v>114</v>
@@ -6139,10 +6139,10 @@
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.45">
       <c r="M4" s="10">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P4" s="10" t="s">
         <v>82</v>
@@ -6154,11 +6154,11 @@
     <row r="5" spans="1:41" x14ac:dyDescent="0.45">
       <c r="D5" s="30" t="str">
         <f>VLOOKUP($D$3,$C$9:$F$999,COLUMN()-2,FALSE)</f>
-        <v>high</v>
+        <v>base</v>
       </c>
       <c r="E5" s="30">
         <f>VLOOKUP($D$3,$C$9:$F$999,COLUMN()-2,FALSE)</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F5" s="30" t="str">
         <f>VLOOKUP($D$3,$C$9:$F$999,COLUMN()-2,FALSE)</f>
@@ -6169,20 +6169,20 @@
         <v>1</v>
       </c>
       <c r="M5" s="10">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.45">
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
       <c r="M6" s="10">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.45">
@@ -6191,6 +6191,12 @@
       </c>
       <c r="F7" s="31"/>
       <c r="G7" s="31"/>
+      <c r="M7" s="10">
+        <v>600</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:41" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="4" t="s">
@@ -6477,7 +6483,7 @@
         <v>high·$100·Y·100%</v>
       </c>
       <c r="C14">
-        <f t="shared" ref="C14:C40" si="2">C13+1</f>
+        <f t="shared" ref="C14:C48" si="2">C13+1</f>
         <v>6</v>
       </c>
       <c r="D14" t="s">
@@ -6498,7 +6504,7 @@
       </c>
       <c r="J14" s="3" t="str">
         <f>VLOOKUP($D$5,$P$3:$Q$5,2,FALSE)</f>
-        <v>C7</v>
+        <v>C3</v>
       </c>
       <c r="K14" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,Veda!$E$5,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
@@ -6506,27 +6512,27 @@
       </c>
       <c r="L14" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="M14" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="N14" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
-        <v>2.2200000000000002</v>
+        <v>1.81</v>
       </c>
       <c r="O14" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
-        <v>2.61</v>
+        <v>2.12</v>
       </c>
       <c r="P14" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
-        <v>3.26</v>
+        <v>2.57</v>
       </c>
       <c r="Q14" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I14)</f>
-        <v>3.56</v>
+        <v>2.85</v>
       </c>
       <c r="V14" s="8">
         <f>U11</f>
@@ -6534,27 +6540,27 @@
       </c>
       <c r="W14" s="8">
         <f t="shared" ref="W14:AB14" si="4">$U$11*L14</f>
-        <v>2445.7275</v>
+        <v>2228.3294999999998</v>
       </c>
       <c r="X14" s="8">
         <f t="shared" si="4"/>
-        <v>3097.9214999999999</v>
+        <v>2789.9409999999998</v>
       </c>
       <c r="Y14" s="8">
         <f t="shared" si="4"/>
-        <v>4021.8629999999998</v>
+        <v>3279.0864999999999</v>
       </c>
       <c r="Z14" s="8">
         <f t="shared" si="4"/>
-        <v>4728.4064999999991</v>
+        <v>3840.6979999999999</v>
       </c>
       <c r="AA14" s="8">
         <f t="shared" si="4"/>
-        <v>5905.9789999999994</v>
+        <v>4655.9404999999997</v>
       </c>
       <c r="AB14" s="8">
         <f t="shared" si="4"/>
-        <v>6449.4739999999993</v>
+        <v>5163.2024999999994</v>
       </c>
       <c r="AI14">
         <v>6</v>
@@ -6605,27 +6611,27 @@
       </c>
       <c r="L15" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
-        <v>1.23</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="M15" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
-        <v>1.3</v>
+        <v>3.28</v>
       </c>
       <c r="N15" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
-        <v>2.71</v>
+        <v>7.17</v>
       </c>
       <c r="O15" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
-        <v>2.94</v>
+        <v>7.35</v>
       </c>
       <c r="P15" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
-        <v>5.92</v>
+        <v>13.56</v>
       </c>
       <c r="Q15" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I15)</f>
-        <v>5.41</v>
+        <v>13.44</v>
       </c>
       <c r="AI15">
         <v>7</v>
@@ -6806,7 +6812,7 @@
       </c>
       <c r="K18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I18)</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I18)</f>
@@ -6814,7 +6820,7 @@
       </c>
       <c r="M18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I18)</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="N18" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I18)</f>
@@ -6837,7 +6843,7 @@
       </c>
       <c r="V18" s="6">
         <f t="shared" ref="V18:AB20" si="7">K18*V$14</f>
-        <v>18.116499999999998</v>
+        <v>0</v>
       </c>
       <c r="W18" s="6">
         <f t="shared" si="7"/>
@@ -6845,23 +6851,23 @@
       </c>
       <c r="X18" s="6">
         <f t="shared" si="7"/>
-        <v>30.979215</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="6">
         <f t="shared" si="7"/>
-        <v>40.218629999999997</v>
+        <v>32.790864999999997</v>
       </c>
       <c r="Z18" s="6">
         <f t="shared" si="7"/>
-        <v>94.568129999999982</v>
+        <v>76.813959999999994</v>
       </c>
       <c r="AA18" s="6">
         <f t="shared" si="7"/>
-        <v>118.11957999999998</v>
+        <v>93.118809999999996</v>
       </c>
       <c r="AB18" s="6">
         <f t="shared" si="7"/>
-        <v>193.48421999999997</v>
+        <v>154.89607499999997</v>
       </c>
       <c r="AC18" t="s">
         <v>17</v>
@@ -6910,62 +6916,62 @@
       </c>
       <c r="K19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="L19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="M19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
-        <v>0.52</v>
+        <v>0.46</v>
       </c>
       <c r="N19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="O19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="P19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q19" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I19)</f>
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="U19" s="10" t="s">
         <v>19</v>
       </c>
       <c r="V19" s="6">
         <f t="shared" si="7"/>
-        <v>960.17449999999997</v>
+        <v>887.70849999999996</v>
       </c>
       <c r="W19" s="6">
         <f t="shared" si="7"/>
-        <v>1222.86375</v>
+        <v>1091.881455</v>
       </c>
       <c r="X19" s="6">
         <f t="shared" si="7"/>
-        <v>1610.9191800000001</v>
+        <v>1283.3728599999999</v>
       </c>
       <c r="Y19" s="6">
         <f t="shared" si="7"/>
-        <v>2010.9314999999999</v>
+        <v>1573.9615199999998</v>
       </c>
       <c r="Z19" s="6">
         <f t="shared" si="7"/>
-        <v>2222.3510549999996</v>
+        <v>1766.72108</v>
       </c>
       <c r="AA19" s="6">
         <f t="shared" si="7"/>
-        <v>2775.8101299999994</v>
+        <v>2234.8514399999999</v>
       </c>
       <c r="AB19" s="6">
         <f t="shared" si="7"/>
-        <v>2902.2632999999996</v>
+        <v>2426.7051749999996</v>
       </c>
       <c r="AC19" t="s">
         <v>17</v>
@@ -7013,62 +7019,62 @@
       </c>
       <c r="K20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="L20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="M20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="N20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="O20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="P20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="Q20" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I20)</f>
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="U20" s="10" t="s">
         <v>22</v>
       </c>
       <c r="V20" s="6">
         <f t="shared" si="7"/>
-        <v>815.24249999999995</v>
+        <v>833.35899999999992</v>
       </c>
       <c r="W20" s="6">
         <f t="shared" si="7"/>
-        <v>1100.5773750000001</v>
+        <v>1047.3148649999998</v>
       </c>
       <c r="X20" s="6">
         <f t="shared" si="7"/>
-        <v>1363.08546</v>
+        <v>1255.47345</v>
       </c>
       <c r="Y20" s="6">
         <f t="shared" si="7"/>
-        <v>1769.6197199999999</v>
+        <v>1475.588925</v>
       </c>
       <c r="Z20" s="6">
         <f t="shared" si="7"/>
-        <v>2127.7829249999995</v>
+        <v>1805.1280599999998</v>
       </c>
       <c r="AA20" s="6">
         <f t="shared" si="7"/>
-        <v>2716.7503399999996</v>
+        <v>2048.61382</v>
       </c>
       <c r="AB20" s="6">
         <f t="shared" si="7"/>
-        <v>3031.2527799999993</v>
+        <v>2271.8090999999999</v>
       </c>
       <c r="AC20" t="s">
         <v>17</v>
@@ -7121,7 +7127,7 @@
       </c>
       <c r="L21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$I21)</f>
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="M21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I21)</f>
@@ -7133,15 +7139,15 @@
       </c>
       <c r="O21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I21)</f>
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="P21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I21)</f>
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="Q21" s="11">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$14,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I21)</f>
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="U21" s="10" t="s">
         <v>24</v>
@@ -7215,31 +7221,31 @@
       </c>
       <c r="V22" s="6">
         <f t="shared" ref="V22:AB22" si="10">V14-SUM(V19:V21)</f>
-        <v>0</v>
+        <v>54.349500000000035</v>
       </c>
       <c r="W22" s="6">
         <f t="shared" si="10"/>
-        <v>86.053374999999505</v>
+        <v>52.900179999999636</v>
       </c>
       <c r="X22" s="6">
         <f t="shared" si="10"/>
-        <v>87.68385999999964</v>
+        <v>214.86168999999973</v>
       </c>
       <c r="Y22" s="6">
         <f t="shared" si="10"/>
-        <v>205.07877999999982</v>
+        <v>193.30305499999986</v>
       </c>
       <c r="Z22" s="6">
         <f t="shared" si="10"/>
-        <v>342.03952000000027</v>
+        <v>232.61585999999988</v>
       </c>
       <c r="AA22" s="6">
         <f t="shared" si="10"/>
-        <v>377.18553000000065</v>
+        <v>336.24223999999958</v>
       </c>
       <c r="AB22" s="6">
         <f t="shared" si="10"/>
-        <v>479.72491999999966</v>
+        <v>428.4552249999997</v>
       </c>
       <c r="AC22" t="s">
         <v>17</v>
@@ -7342,8 +7348,8 @@
         <v>26</v>
       </c>
       <c r="J24" s="3" t="str">
-        <f>VLOOKUP(E5,$M$3:$N$6,2,FALSE)</f>
-        <v>C7</v>
+        <f>VLOOKUP(E5,$M$3:$N$7,2,FALSE)</f>
+        <v>C1</v>
       </c>
       <c r="K24" s="8">
         <v>0</v>
@@ -7353,23 +7359,23 @@
       </c>
       <c r="M24" s="8">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$24,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$I24)</f>
-        <v>0</v>
+        <v>176.95</v>
       </c>
       <c r="N24" s="8">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$24,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$I24)</f>
-        <v>0</v>
+        <v>242.69</v>
       </c>
       <c r="O24" s="8">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$24,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$I24)</f>
-        <v>0</v>
+        <v>325.37</v>
       </c>
       <c r="P24" s="8">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$24,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$I24)</f>
-        <v>0</v>
+        <v>430.26</v>
       </c>
       <c r="Q24" s="8">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$J$24,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$I24)</f>
-        <v>0</v>
+        <v>592.32000000000005</v>
       </c>
       <c r="U24" s="26" t="s">
         <v>27</v>
@@ -7380,23 +7386,23 @@
       </c>
       <c r="X24" s="28">
         <f>M24/1000</f>
-        <v>0</v>
+        <v>0.17695</v>
       </c>
       <c r="Y24" s="28">
         <f>N24/1000</f>
-        <v>0</v>
+        <v>0.24268999999999999</v>
       </c>
       <c r="Z24" s="28">
         <f>O24/1000</f>
-        <v>0</v>
+        <v>0.32536999999999999</v>
       </c>
       <c r="AA24" s="28">
         <f>P24/1000</f>
-        <v>0</v>
+        <v>0.43025999999999998</v>
       </c>
       <c r="AB24" s="28">
         <f>Q24/1000</f>
-        <v>0</v>
+        <v>0.59232000000000007</v>
       </c>
       <c r="AC24" s="29" t="s">
         <v>28</v>
@@ -8090,18 +8096,87 @@
       </c>
     </row>
     <row r="41" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A41">
+        <v>6</v>
+      </c>
+      <c r="B41" t="str">
+        <f t="shared" ref="B41:B48" si="15">_xlfn.TEXTJOIN(CHAR(183),TRUE,D41,TEXT(E41,"$000"),F41,TEXT(G41,"000%"))</f>
+        <v>base·$600·Y·100%</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="D41" t="s">
+        <v>114</v>
+      </c>
+      <c r="E41">
+        <v>600</v>
+      </c>
+      <c r="F41" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G41" s="33">
+        <v>1</v>
+      </c>
       <c r="AL41" s="10">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A42">
+        <v>7</v>
+      </c>
+      <c r="B42" t="str">
+        <f t="shared" si="15"/>
+        <v>high·$600·Y·100%</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="D42" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42">
+        <v>600</v>
+      </c>
+      <c r="F42" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G42" s="33">
+        <v>1</v>
+      </c>
       <c r="AL42" s="10">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A43">
+        <v>8</v>
+      </c>
+      <c r="B43" t="str">
+        <f t="shared" si="15"/>
+        <v>base·$600·N·100%</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="D43" t="s">
+        <v>114</v>
+      </c>
+      <c r="E43">
+        <v>600</v>
+      </c>
+      <c r="F43" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G43" s="33">
+        <v>1</v>
+      </c>
       <c r="I43" t="s">
         <v>101</v>
       </c>
@@ -8111,6 +8186,29 @@
       </c>
     </row>
     <row r="44" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A44">
+        <v>9</v>
+      </c>
+      <c r="B44" t="str">
+        <f t="shared" si="15"/>
+        <v>high·$600·N·100%</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="2"/>
+        <v>36</v>
+      </c>
+      <c r="D44" t="s">
+        <v>82</v>
+      </c>
+      <c r="E44">
+        <v>600</v>
+      </c>
+      <c r="F44" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G44" s="33">
+        <v>1</v>
+      </c>
       <c r="I44" t="s">
         <v>13</v>
       </c>
@@ -8125,23 +8223,23 @@
         <v>2025</v>
       </c>
       <c r="M44">
-        <f t="shared" ref="M44:Q44" si="15">M17</f>
+        <f t="shared" ref="M44:Q44" si="16">M17</f>
         <v>2030</v>
       </c>
       <c r="N44">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2035</v>
       </c>
       <c r="O44">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2040</v>
       </c>
       <c r="P44">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2045</v>
       </c>
       <c r="Q44">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2050</v>
       </c>
       <c r="T44" t="s">
@@ -8156,6 +8254,30 @@
       </c>
     </row>
     <row r="45" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A45">
+        <v>10</v>
+      </c>
+      <c r="B45" t="str">
+        <f t="shared" si="15"/>
+        <v>base·$600·Y·001%</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="2"/>
+        <v>37</v>
+      </c>
+      <c r="D45" t="s">
+        <v>114</v>
+      </c>
+      <c r="E45">
+        <v>600</v>
+      </c>
+      <c r="F45" s="33" t="str">
+        <f>F41</f>
+        <v>Y</v>
+      </c>
+      <c r="G45" s="33">
+        <v>0.01</v>
+      </c>
       <c r="I45" t="s">
         <v>77</v>
       </c>
@@ -8168,27 +8290,27 @@
         <v>30.9</v>
       </c>
       <c r="L45">
-        <f t="shared" ref="L45:Q45" si="16">AVERAGE($T45)*L37</f>
+        <f t="shared" ref="L45:Q45" si="17">AVERAGE($T45)*L37</f>
         <v>32.136000000000003</v>
       </c>
       <c r="M45">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>33.99</v>
       </c>
       <c r="N45">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>33.372</v>
       </c>
       <c r="O45">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>38.315999999999995</v>
       </c>
       <c r="P45">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>40.17</v>
       </c>
       <c r="Q45">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>41.097000000000001</v>
       </c>
       <c r="T45">
@@ -8205,39 +8327,63 @@
       </c>
     </row>
     <row r="46" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A46">
+        <v>11</v>
+      </c>
+      <c r="B46" t="str">
+        <f t="shared" si="15"/>
+        <v>high·$600·Y·001%</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="2"/>
+        <v>38</v>
+      </c>
+      <c r="D46" t="s">
+        <v>82</v>
+      </c>
+      <c r="E46">
+        <v>600</v>
+      </c>
+      <c r="F46" s="33" t="str">
+        <f t="shared" ref="F46:F48" si="18">F42</f>
+        <v>Y</v>
+      </c>
+      <c r="G46" s="33">
+        <v>0.01</v>
+      </c>
       <c r="I46" t="s">
         <v>78</v>
       </c>
       <c r="J46" t="str">
-        <f t="shared" ref="J46:J48" si="17">I46</f>
+        <f t="shared" ref="J46:J48" si="19">I46</f>
         <v>Coal</v>
       </c>
       <c r="K46">
-        <f t="shared" ref="K46:Q48" si="18">AVERAGE($T46:$U46)*K38</f>
+        <f t="shared" ref="K46:Q48" si="20">AVERAGE($T46:$U46)*K38</f>
         <v>9.8000000000000007</v>
       </c>
       <c r="L46">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>10.388000000000002</v>
       </c>
       <c r="M46">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>11.074</v>
       </c>
       <c r="N46">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>11.465999999999999</v>
       </c>
       <c r="O46">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>11.956000000000001</v>
       </c>
       <c r="P46">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>12.348000000000001</v>
       </c>
       <c r="Q46">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>12.740000000000002</v>
       </c>
       <c r="T46">
@@ -8254,39 +8400,63 @@
       </c>
     </row>
     <row r="47" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A47">
+        <v>12</v>
+      </c>
+      <c r="B47" t="str">
+        <f t="shared" si="15"/>
+        <v>base·$600·N·001%</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="D47" t="s">
+        <v>114</v>
+      </c>
+      <c r="E47">
+        <v>600</v>
+      </c>
+      <c r="F47" s="33" t="str">
+        <f t="shared" si="18"/>
+        <v>N</v>
+      </c>
+      <c r="G47" s="33">
+        <v>0.01</v>
+      </c>
       <c r="I47" t="s">
         <v>79</v>
       </c>
       <c r="J47" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>Oil</v>
       </c>
       <c r="K47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>50</v>
       </c>
       <c r="L47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>54</v>
       </c>
       <c r="M47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>56.999999999999993</v>
       </c>
       <c r="N47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>60</v>
       </c>
       <c r="O47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>63.5</v>
       </c>
       <c r="P47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>65</v>
       </c>
       <c r="Q47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>66</v>
       </c>
       <c r="T47">
@@ -8303,15 +8473,39 @@
       </c>
     </row>
     <row r="48" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="A48">
+        <v>13</v>
+      </c>
+      <c r="B48" t="str">
+        <f t="shared" si="15"/>
+        <v>high·$600·N·001%</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="D48" t="s">
+        <v>82</v>
+      </c>
+      <c r="E48">
+        <v>600</v>
+      </c>
+      <c r="F48" s="33" t="str">
+        <f t="shared" si="18"/>
+        <v>N</v>
+      </c>
+      <c r="G48" s="33">
+        <v>0.01</v>
+      </c>
       <c r="I48" t="s">
         <v>80</v>
       </c>
       <c r="J48" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>Bioenergy</v>
       </c>
       <c r="K48">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>18.5</v>
       </c>
       <c r="Q48">
@@ -8583,6 +8777,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="M3:N7">
+    <sortCondition ref="M3:M7"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFDA3B42-376B-4FE8-9FC8-16D7A15856B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D1CEE6C-2B30-48B3-91B4-91D0F6D49FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8097,7 +8097,7 @@
     </row>
     <row r="41" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" ref="B41:B48" si="15">_xlfn.TEXTJOIN(CHAR(183),TRUE,D41,TEXT(E41,"$000"),F41,TEXT(G41,"000%"))</f>
@@ -8126,7 +8126,7 @@
     </row>
     <row r="42" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="15"/>
@@ -8155,7 +8155,7 @@
     </row>
     <row r="43" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A43">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="15"/>
@@ -8187,7 +8187,7 @@
     </row>
     <row r="44" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A44">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="15"/>
@@ -8255,7 +8255,7 @@
     </row>
     <row r="45" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A45">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="15"/>
@@ -8328,7 +8328,7 @@
     </row>
     <row r="46" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A46">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="15"/>
@@ -8401,7 +8401,7 @@
     </row>
     <row r="47" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A47">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="15"/>
@@ -8474,7 +8474,7 @@
     </row>
     <row r="48" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A48">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="15"/>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D1CEE6C-2B30-48B3-91B4-91D0F6D49FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE7092F-A31A-47DC-BF4B-51B2F2BB7CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -517,7 +517,7 @@
     <t>aggregators,grid</t>
   </si>
   <si>
-    <t>33-40</t>
+    <t>1-40</t>
   </si>
 </sst>
 </file>
@@ -6109,7 +6109,7 @@
     <row r="2" spans="1:41" x14ac:dyDescent="0.45">
       <c r="D2" s="1" t="str">
         <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,I1:EG1)</f>
-        <v>~Inputcell: 33-40</v>
+        <v>~Inputcell: 1-40</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>26</v>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE7092F-A31A-47DC-BF4B-51B2F2BB7CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999B5BCC-3433-4A4C-97DA-8844927F6AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1816" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="150">
   <si>
     <t>C1</t>
   </si>
@@ -517,7 +517,16 @@
     <t>aggregators,grid</t>
   </si>
   <si>
-    <t>1-40</t>
+    <t>ncap_pkcnt</t>
+  </si>
+  <si>
+    <t>distr_sol*</t>
+  </si>
+  <si>
+    <t>distr_wo*</t>
+  </si>
+  <si>
+    <t>1-32</t>
   </si>
 </sst>
 </file>
@@ -6103,13 +6112,13 @@
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.45">
       <c r="I1" s="21" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.45">
       <c r="D2" s="1" t="str">
         <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,I1:EG1)</f>
-        <v>~Inputcell: 1-40</v>
+        <v>~Inputcell: 1-32</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>26</v>
@@ -8789,7 +8798,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CD5270F-E5C6-4B02-8A48-7D871D6014E5}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
@@ -8838,120 +8847,142 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="C8" t="str">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E6" t="s">
+        <v>147</v>
+      </c>
+      <c r="F6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C7" t="s">
+        <v>146</v>
+      </c>
+      <c r="E7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F7">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C11" t="str">
         <f>IF($A$1="Y","DEF active","~TFM_INS: limtype=LO")</f>
         <v>DEF active</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="C9" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C12" t="s">
         <v>14</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D12" t="s">
         <v>131</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E12" t="s">
         <v>36</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F12" t="s">
         <v>128</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G12" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="C10" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C13" t="s">
         <v>133</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D13" t="s">
         <v>134</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
         <v>-13</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G13" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="C11" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C14" t="s">
         <v>136</v>
       </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
         <v>-13</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G14" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="C14" t="str">
+    <row r="17" spans="3:6" x14ac:dyDescent="0.45">
+      <c r="C17" t="str">
         <f>IF($A$1="Y","DEF active","~TFM_UPD")</f>
         <v>DEF active</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="C15" t="s">
+    <row r="18" spans="3:6" x14ac:dyDescent="0.45">
+      <c r="C18" t="s">
         <v>14</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D18" t="s">
         <v>141</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E18" t="s">
         <v>138</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F18" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="C16" t="s">
+    <row r="19" spans="3:6" x14ac:dyDescent="0.45">
+      <c r="C19" t="s">
         <v>140</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D19" t="s">
         <v>139</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E19" t="s">
         <v>139</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="3:5" x14ac:dyDescent="0.45">
-      <c r="C20" t="str">
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:6" x14ac:dyDescent="0.45">
+      <c r="C23" t="str">
         <f>IF($A$2=1,"Tx cost 100%","~TFM_UPD")</f>
         <v>Tx cost 100%</v>
       </c>
     </row>
-    <row r="21" spans="3:5" x14ac:dyDescent="0.45">
-      <c r="C21" t="s">
+    <row r="24" spans="3:6" x14ac:dyDescent="0.45">
+      <c r="C24" t="s">
         <v>14</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D24" t="s">
         <v>128</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E24" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="3:5" x14ac:dyDescent="0.45">
-      <c r="C22" t="s">
+    <row r="25" spans="3:6" x14ac:dyDescent="0.45">
+      <c r="C25" t="s">
         <v>143</v>
       </c>
-      <c r="D22" t="str">
+      <c r="D25" t="str">
         <f>"*"&amp;A2</f>
         <v>*1</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E25" t="s">
         <v>145</v>
       </c>
     </row>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999B5BCC-3433-4A4C-97DA-8844927F6AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A33CAF4-CBDA-4F83-A235-3C2A6D8C61CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1816" uniqueCount="147">
   <si>
     <t>C1</t>
   </si>
@@ -517,16 +517,7 @@
     <t>aggregators,grid</t>
   </si>
   <si>
-    <t>ncap_pkcnt</t>
-  </si>
-  <si>
-    <t>distr_sol*</t>
-  </si>
-  <si>
-    <t>distr_wo*</t>
-  </si>
-  <si>
-    <t>1-32</t>
+    <t>1-40</t>
   </si>
 </sst>
 </file>
@@ -6112,13 +6103,13 @@
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.45">
       <c r="I1" s="21" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.45">
       <c r="D2" s="1" t="str">
         <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,I1:EG1)</f>
-        <v>~Inputcell: 1-32</v>
+        <v>~Inputcell: 1-40</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>26</v>
@@ -8845,28 +8836,6 @@
       </c>
       <c r="F5">
         <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="C6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E6" t="s">
-        <v>147</v>
-      </c>
-      <c r="F6">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="C7" t="s">
-        <v>146</v>
-      </c>
-      <c r="E7" t="s">
-        <v>148</v>
-      </c>
-      <c r="F7">
-        <v>0.35</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
